--- a/data/kpi-model/Owner-KPI-Model.xlsx
+++ b/data/kpi-model/Owner-KPI-Model.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calculated vs Shown'!$A$1:$I$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Owner KPIs'!$A$1:$N$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Owner Screens'!$A$1:$J$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Owner Screens'!$A$1:$J$173</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Entity Inputs'!$A$3:$FU$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Plant Inputs'!$A$3:$BY$39</definedName>
   </definedNames>
@@ -682,7 +682,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>98.1 % of plan</t>
+          <t>95.5 % of plan</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>O-01, O-09, S-03 · Owner view, S-10, STATE GALLERY · O-01 + S-02, O-01 · large display ≥ 1600</t>
+          <t>O-01, O-01 · large display ≥ 1600, O-09, S-03 · Owner view, S-10, STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>83.4 %</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>O-01, STATE GALLERY · O-01 + S-02, O-01 · large display ≥ 1600</t>
+          <t>O-01, O-01 · large display ≥ 1600, O-09, STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>205 h</t>
+          <t>270 h</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>3.6 h</t>
+          <t>7.8 h</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>3.1 % of hours</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Different</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>95.6 %</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>412 ₹ /t; ₹412 /t</t>
+          <t>2,934 ₹/t</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1004,17 +1004,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>₹214 /t</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Different</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>9.8 ₹/t</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Different</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>O-05, O-09</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0.82 tCO2e/t</t>
+          <t>427.7 kt CO2e</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>O-05, O-09</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>O-09, S-10</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>O-01, O-09</t>
+          <t>O-01</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1740,17 +1740,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>78.4 %</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Different</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>6.1 ₹/t</t>
+          <t>174 ₹/t</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>91 %; 91%</t>
+          <t>91.4 %</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Different</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -3856,17 +3856,17 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Different</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -3902,17 +3902,17 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Different</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>O-01, O-02, O-09, S-10, STATE GALLERY · O-01 + S-02, O-01 · large display ≥ 1600</t>
+          <t>O-01, O-01 · large display ≥ 1600, O-02, S-10, STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -6018,17 +6018,17 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>11.2 kt</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>Different</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
@@ -6064,17 +6064,17 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>Different</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>98.1 % of plan (O-01, O-09, STATE GALLERY); 103.2 % of plan (flash) (S-03); 100.2 % of plan (S-10)</t>
+          <t>98.1 % of plan (O-01, STATE GALLERY); 103.2 % of plan (flash) (S-03); 100.2 % of plan (S-10); 95.5 % of plan (O-09)</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>O-01, O-09, S-03 · Owner view, S-10, STATE GALLERY · O-01 + S-02, O-01 · large display ≥ 1600</t>
+          <t>O-01, O-01 · large display ≥ 1600, O-09, S-03 · Owner view, S-10, STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>86% (O-01, STATE GALLERY)</t>
+          <t>86% (O-01, STATE GALLERY); 83.4 % (O-09)</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>O-01, STATE GALLERY · O-01 + S-02, O-01 · large display ≥ 1600</t>
+          <t>O-01, O-01 · large display ≥ 1600, O-09, STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>205 h (O-09)</t>
+          <t>270 h (O-09)</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>3.6 h (O-09)</t>
+          <t>7.8 h (O-09)</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>3.1 % of hours (O-09)</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>93% (O-09)</t>
+          <t>95.6 % (O-09)</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>412 ₹ /t (O-09); ₹412 /t (O-09)</t>
+          <t>2,934 ₹/t (O-09)</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>₹214 /t (O-09)</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>9.8 ₹/t (O-09)</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>3.1 m³/t (O-05, O-09)</t>
+          <t>3.1 m³/t (O-05)</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>O-05, O-09</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>0.82 tCO2e/t (O-05, O-09)</t>
+          <t>0.82 tCO2e/t (O-05); 427.7 kt CO2e (O-09)</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>5.2 GJ/t (O-05, O-09)</t>
+          <t>5.2 GJ/t (O-05)</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>O-05, O-09</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -7091,12 +7091,12 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>3.5 days of cover (O-09, S-10)</t>
+          <t>3.5 days of cover (S-10)</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>O-09, S-10</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -7685,12 +7685,12 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>86% (O-01); 86 % (O-09)</t>
+          <t>86% (O-01)</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>O-01, O-09</t>
+          <t>O-01</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>78.4 % (O-09)</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>6.1 ₹/t (O-09)</t>
+          <t>174 ₹/t (O-09)</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>91 % (O-09); 91% (O-09)</t>
+          <t>91.4 % (O-09)</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>38% (O-09)</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
@@ -10853,12 +10853,12 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>0 (O-09)</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -13559,12 +13559,12 @@
       </c>
       <c r="L113" s="3" t="inlineStr">
         <is>
-          <t>4 days (O-01, O-02, O-09, S-10, STATE GALLERY)</t>
+          <t>4 days (O-01, O-02, S-10, STATE GALLERY)</t>
         </is>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>O-01, O-02, O-09, S-10, STATE GALLERY · O-01 + S-02, O-01 · large display ≥ 1600</t>
+          <t>O-01, O-01 · large display ≥ 1600, O-02, S-10, STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>11.2 kt (O-09)</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N118" s="3" t="inlineStr">
@@ -13955,12 +13955,12 @@
       </c>
       <c r="L119" s="3" t="inlineStr">
         <is>
-          <t>41% (O-09)</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N119" s="3" t="inlineStr">
@@ -13981,7 +13981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J183"/>
+  <dimension ref="A1:J173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.7109375" customWidth="1" min="1" max="1"/>
@@ -18547,7 +18547,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -18557,7 +18557,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Group MTD</t>
+          <t>Production vs plan · Group</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -18572,13 +18572,10 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>98.1 % of plan</t>
-        </is>
-      </c>
-      <c r="I94" s="21">
-        <f>'Owner KPIs'!K2</f>
-        <v/>
-      </c>
+          <t>95.5 % of plan</t>
+        </is>
+      </c>
+      <c r="I94" s="21" t="n"/>
       <c r="J94" s="3" t="inlineStr">
         <is>
           <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
@@ -18596,7 +18593,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -18606,12 +18603,12 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>MTBF · critical assets</t>
+          <t>Production vs plan · Entity A1 (A1)</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>REL-001</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -18621,16 +18618,13 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>205 h</t>
-        </is>
-      </c>
-      <c r="I95" s="21">
-        <f>'Owner KPIs'!K4</f>
-        <v/>
-      </c>
+          <t>91.3 % of plan</t>
+        </is>
+      </c>
+      <c r="I95" s="21" t="n"/>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 4 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18645,7 +18639,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -18655,12 +18649,12 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Conversion cost per tonne</t>
+          <t>Production vs plan · Entity A2 (A2)</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>CST-001</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -18670,16 +18664,13 @@
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>412 ₹ /t</t>
-        </is>
-      </c>
-      <c r="I96" s="21">
-        <f>'Owner KPIs'!K8</f>
-        <v/>
-      </c>
+          <t>100.3 % of plan</t>
+        </is>
+      </c>
+      <c r="I96" s="21" t="n"/>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 8 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18694,7 +18685,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -18709,7 +18700,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>OPS-005</t>
+          <t>OPS-003</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -18719,16 +18710,13 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>86 %</t>
-        </is>
-      </c>
-      <c r="I97" s="21">
-        <f>'Owner KPIs'!K24</f>
-        <v/>
-      </c>
+          <t>83.4 %</t>
+        </is>
+      </c>
+      <c r="I97" s="21" t="n"/>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 24 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18731,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -18753,12 +18741,12 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>OEE · Group weighted</t>
+          <t>MTBF · Group</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>OPS-006</t>
+          <t>REL-001</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -18768,16 +18756,13 @@
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>78.4 %</t>
-        </is>
-      </c>
-      <c r="I98" s="21">
-        <f>'Owner KPIs'!K25</f>
-        <v/>
-      </c>
+          <t>270 h</t>
+        </is>
+      </c>
+      <c r="I98" s="21" t="n"/>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 25 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 4 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18792,7 +18777,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -18802,12 +18787,12 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Supplier OTIF · Group</t>
+          <t>Mean time to repair</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>SUP-001</t>
+          <t>REL-002</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -18817,16 +18802,13 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>91 %</t>
-        </is>
-      </c>
-      <c r="I99" s="21">
-        <f>'Owner KPIs'!K70</f>
-        <v/>
-      </c>
+          <t>7.8 h</t>
+        </is>
+      </c>
+      <c r="I99" s="21" t="n"/>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 70 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 5 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18841,22 +18823,22 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>RM-1 days of cover</t>
+          <t>Preventive-maintenance compliance</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>SIG-009</t>
+          <t>REL-005</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -18866,16 +18848,13 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>3.5 days of cover</t>
-        </is>
-      </c>
-      <c r="I100" s="21">
-        <f>'Owner KPIs'!K15</f>
-        <v/>
-      </c>
+          <t>95.6 %</t>
+        </is>
+      </c>
+      <c r="I100" s="21" t="n"/>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 15 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 7 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18890,41 +18869,38 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Days to breach · Plant 02 plan</t>
+          <t>Cost per tonne · Group</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>PRD-001</t>
+          <t>CST-001</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>4 days</t>
-        </is>
-      </c>
-      <c r="I101" s="21">
-        <f>ROUND('Plant Inputs'!BT15,2)</f>
-        <v/>
-      </c>
+          <t>2,934 ₹/t</t>
+        </is>
+      </c>
+      <c r="I101" s="21" t="n"/>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 8 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18939,22 +18915,22 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Production loss from downtime · P07</t>
+          <t>Power cost per tonne</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>PRD-006</t>
+          <t>CST-004</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -18964,16 +18940,13 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>11.2 kt</t>
-        </is>
-      </c>
-      <c r="I102" s="21">
-        <f>'Owner KPIs'!K118</f>
-        <v/>
-      </c>
+          <t>174 ₹/t</t>
+        </is>
+      </c>
+      <c r="I102" s="21" t="n"/>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 118 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 28 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18988,22 +18961,22 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Probability OEE &lt; 78% in P08</t>
+          <t>OEE</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>PRD-007</t>
+          <t>PLT-002</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -19013,18 +18986,11 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>41%</t>
-        </is>
-      </c>
-      <c r="I103" s="21">
-        <f>'Owner KPIs'!K119</f>
-        <v/>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 119 (Group, Sep 2026)</t>
-        </is>
-      </c>
+          <t>84.1 %</t>
+        </is>
+      </c>
+      <c r="I103" s="21" t="n"/>
+      <c r="J103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
@@ -19037,22 +19003,22 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>MTBF · critical assets</t>
+          <t>Supplier on-time delivery</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>REL-001</t>
+          <t>SUP-001</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -19062,16 +19028,13 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>205 h</t>
-        </is>
-      </c>
-      <c r="I104" s="21">
-        <f>'Owner KPIs'!K4</f>
-        <v/>
-      </c>
+          <t>91.4 %</t>
+        </is>
+      </c>
+      <c r="I104" s="21" t="n"/>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 4 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 70 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19086,22 +19049,22 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>MTTR · critical assets</t>
+          <t>Supplier fill rate</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>REL-002</t>
+          <t>SUP-002</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -19111,18 +19074,11 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>3.6 h</t>
-        </is>
-      </c>
-      <c r="I105" s="21">
-        <f>'Owner KPIs'!K5</f>
-        <v/>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 5 (Group, Sep 2026)</t>
-        </is>
-      </c>
+          <t>96.8 %</t>
+        </is>
+      </c>
+      <c r="I105" s="21" t="n"/>
+      <c r="J105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
@@ -19135,22 +19091,22 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Unplanned downtime · P07</t>
+          <t>Emissions</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>REL-003</t>
+          <t>SUS-002</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -19160,16 +19116,13 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>3.1 % of hours</t>
-        </is>
-      </c>
-      <c r="I106" s="21">
-        <f>'Owner KPIs'!K6</f>
-        <v/>
-      </c>
+          <t>427.7 kt CO2e</t>
+        </is>
+      </c>
+      <c r="I106" s="21" t="n"/>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 6 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 12 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19184,22 +19137,22 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>PM compliance</t>
+          <t>Production vs plan</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>REL-005</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -19209,16 +19162,17 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="I107" s="21">
-        <f>'Owner KPIs'!K7</f>
-        <v/>
+          <t>Apr–Sep monthly series</t>
+        </is>
+      </c>
+      <c r="I107" s="21" t="inlineStr">
+        <is>
+          <t>Apr–Sep: None, None, None, None, None, None</t>
+        </is>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 7 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 2 (Group, Apr–Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19233,22 +19187,22 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Conversion cost per tonne</t>
+          <t>Reliability trend · mean time to repair</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>CST-001</t>
+          <t>REL-002</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -19258,16 +19212,17 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>₹412 /t</t>
-        </is>
-      </c>
-      <c r="I108" s="21">
-        <f>'Owner KPIs'!K8</f>
-        <v/>
+          <t>Apr–Sep monthly series</t>
+        </is>
+      </c>
+      <c r="I108" s="21" t="inlineStr">
+        <is>
+          <t>Apr–Sep: None, None, None, None, None, None</t>
+        </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 8 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 5 (Group, Apr–Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19282,22 +19237,22 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Operations Command View</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Variable cost per tonne</t>
+          <t>Sustainability curve · emissions</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>CST-002</t>
+          <t>SUS-002</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -19307,16 +19262,17 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>₹214 /t</t>
-        </is>
-      </c>
-      <c r="I109" s="21">
-        <f>'Owner KPIs'!K9</f>
-        <v/>
+          <t>Apr–Sep monthly series</t>
+        </is>
+      </c>
+      <c r="I109" s="21" t="inlineStr">
+        <is>
+          <t>Apr–Sep: None, None, None, None, None, None</t>
+        </is>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 9 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 12 (Group, Apr–Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19326,27 +19282,27 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Fuel cost per tonne</t>
+          <t>Leadership KPIs affected by findings</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>CST-003</t>
+          <t>GOV-007</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -19356,16 +19312,16 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>9.8 ₹/t</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I110" s="21">
-        <f>'Owner KPIs'!K10</f>
+        <f>'Owner KPIs'!K96</f>
         <v/>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 10 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 96 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19375,27 +19331,27 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Water usage</t>
+          <t>Material reconciliation breaks</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>SUS-001</t>
+          <t>TRU-007</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -19405,16 +19361,16 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>3.1 m³/t</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I111" s="21">
-        <f>'Owner KPIs'!K11</f>
+        <f>'Owner KPIs'!K97</f>
         <v/>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 11 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 97 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19424,27 +19380,27 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>Certified KPI percentage</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>SUS-002</t>
+          <t>TRU-001</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -19454,16 +19410,16 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>0.82 tCO2e/t</t>
+          <t>84 % of leadership KPIs</t>
         </is>
       </c>
       <c r="I112" s="21">
-        <f>'Owner KPIs'!K12</f>
+        <f>'Owner KPIs'!K100</f>
         <v/>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 12 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 100 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19473,27 +19429,27 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Energy intensity</t>
+          <t>Uncertified KPI count</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>SUS-003</t>
+          <t>TRU-002</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -19503,16 +19459,16 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>5.2 GJ/t</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I113" s="21">
-        <f>'Owner KPIs'!K13</f>
+        <f>'Owner KPIs'!K101</f>
         <v/>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 13 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 101 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19522,27 +19478,27 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Critical-material cover · RM-1</t>
+          <t>Flash-to-Close variance (P06)</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>SIG-009</t>
+          <t>TRU-010</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -19552,16 +19508,16 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>3.5 days of cover</t>
+          <t>0.6 %</t>
         </is>
       </c>
       <c r="I114" s="21">
-        <f>'Owner KPIs'!K15</f>
+        <f>'Owner KPIs'!K104</f>
         <v/>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 15 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 104 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19571,27 +19527,27 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Power cost per tonne</t>
+          <t>Variance against Board numbers</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>CST-004</t>
+          <t>TRU-011</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -19601,16 +19557,16 @@
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>6.1 ₹/t</t>
+          <t>0.3 % (max abs)</t>
         </is>
       </c>
       <c r="I115" s="21">
-        <f>'Owner KPIs'!K28</f>
+        <f>'Owner KPIs'!K105</f>
         <v/>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 28 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 105 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19620,12 +19576,12 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -19635,12 +19591,12 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Supplier OTIF</t>
+          <t>Ageing certification approvals</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>SUP-001</t>
+          <t>GOV-001</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -19650,16 +19606,16 @@
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>2 &gt; [PH] d</t>
         </is>
       </c>
       <c r="I116" s="21">
-        <f>'Owner KPIs'!K70</f>
+        <f>'Owner KPIs'!K90</f>
         <v/>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 70 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 90 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19669,12 +19625,12 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -19684,12 +19640,12 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Single-source spend share</t>
+          <t>Override count (KPI)</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>SUP-007</t>
+          <t>GOV-002</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -19699,16 +19655,16 @@
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I117" s="21">
-        <f>'Owner KPIs'!K71</f>
+        <f>'Owner KPIs'!K91</f>
         <v/>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 71 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 91 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19718,12 +19674,12 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -19733,12 +19689,12 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Supplier EHS incidents YTD</t>
+          <t>Recurring data-quality issues</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>SUP-008</t>
+          <t>GOV-003</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -19748,16 +19704,16 @@
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I118" s="21">
-        <f>'Owner KPIs'!K72</f>
+        <f>'Owner KPIs'!K92</f>
         <v/>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 72 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 92 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19767,12 +19723,12 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Operations and Assets</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -19782,12 +19738,12 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Production loss from downtime</t>
+          <t>Open audit findings</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>PRD-006</t>
+          <t>GOV-004</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -19797,16 +19753,16 @@
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>11.2 kt</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I119" s="21">
-        <f>'Owner KPIs'!K118</f>
+        <f>'Owner KPIs'!K93</f>
         <v/>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 118 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 93 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19826,17 +19782,17 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Leadership KPIs affected by findings</t>
+          <t>Overdue assurance actions</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>GOV-007</t>
+          <t>GOV-005</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -19846,16 +19802,16 @@
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I120" s="21">
-        <f>'Owner KPIs'!K96</f>
+        <f>'Owner KPIs'!K94</f>
         <v/>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 96 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 94 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19875,17 +19831,17 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Material reconciliation breaks</t>
+          <t>Repeat findings</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>TRU-007</t>
+          <t>GOV-006</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -19899,12 +19855,12 @@
         </is>
       </c>
       <c r="I121" s="21">
-        <f>'Owner KPIs'!K97</f>
+        <f>'Owner KPIs'!K95</f>
         <v/>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 97 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 95 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19924,17 +19880,17 @@
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Certified KPI percentage</t>
+          <t>Leadership KPIs affected by findings</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>TRU-001</t>
+          <t>GOV-007</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -19944,16 +19900,16 @@
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>84 % of leadership KPIs</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I122" s="21">
-        <f>'Owner KPIs'!K100</f>
+        <f>'Owner KPIs'!K96</f>
         <v/>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 100 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 96 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19973,17 +19929,17 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Uncertified KPI count</t>
+          <t>Evidence completeness rate</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>TRU-002</t>
+          <t>GOV-008</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -19993,16 +19949,16 @@
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="I123" s="21">
-        <f>'Owner KPIs'!K101</f>
+        <f>'Owner KPIs'!K98</f>
         <v/>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 101 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 98 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20022,17 +19978,17 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Flash-to-Close variance (P06)</t>
+          <t>Average finding-closure time</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>TRU-010</t>
+          <t>GOV-009</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -20042,16 +19998,16 @@
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>0.6 %</t>
+          <t>34 d</t>
         </is>
       </c>
       <c r="I124" s="21">
-        <f>'Owner KPIs'!K104</f>
+        <f>'Owner KPIs'!K99</f>
         <v/>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 104 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 99 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20071,17 +20027,17 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Variance against Board numbers</t>
+          <t>KPI certification coverage</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>TRU-011</t>
+          <t>TRU-001</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -20091,16 +20047,16 @@
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>0.3 % (max abs)</t>
+          <t>84 % of leadership KPIs</t>
         </is>
       </c>
       <c r="I125" s="21">
-        <f>'Owner KPIs'!K105</f>
+        <f>'Owner KPIs'!K100</f>
         <v/>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 105 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 100 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20125,12 +20081,12 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Ageing certification approvals</t>
+          <t>Source-to-Lake reconciliation rate</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>GOV-001</t>
+          <t>TRU-008</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -20140,16 +20096,16 @@
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>2 &gt; [PH] d</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="I126" s="21">
-        <f>'Owner KPIs'!K90</f>
+        <f>'Owner KPIs'!K102</f>
         <v/>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 90 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 102 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20174,12 +20130,12 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Override count (KPI)</t>
+          <t>Flash-to-MIS reconciliation rate</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>GOV-002</t>
+          <t>TRU-009</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -20189,16 +20145,16 @@
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="I127" s="21">
-        <f>'Owner KPIs'!K91</f>
+        <f>'Owner KPIs'!K103</f>
         <v/>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 91 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 103 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20223,12 +20179,12 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Recurring data-quality issues</t>
+          <t>Flash-to-Close variance (P06)</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>GOV-003</t>
+          <t>TRU-010</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -20238,16 +20194,16 @@
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.6 %</t>
         </is>
       </c>
       <c r="I128" s="21">
-        <f>'Owner KPIs'!K92</f>
+        <f>'Owner KPIs'!K104</f>
         <v/>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 92 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 104 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20272,12 +20228,12 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Open audit findings</t>
+          <t>Variance against Board numbers</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>GOV-004</t>
+          <t>TRU-011</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -20287,16 +20243,16 @@
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0.3% max abs · Entity B2</t>
         </is>
       </c>
       <c r="I129" s="21">
-        <f>'Owner KPIs'!K93</f>
+        <f>'Owner KPIs'!K105</f>
         <v/>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 93 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 105 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20306,46 +20262,46 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-03 · Owner view</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>KPI Detail and Lineage · OPS-001 Production vs plan · Entity A1</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Overdue assurance actions</t>
+          <t>Production vs plan · Entity A1 MTD</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>GOV-005</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Entity A1</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>103.2 % of plan (flash)</t>
         </is>
       </c>
       <c r="I130" s="21">
-        <f>'Owner KPIs'!K94</f>
+        <f>ROUND(IFERROR(100*'Entity Inputs'!M9/'Entity Inputs'!K9,0),2)</f>
         <v/>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 94 (Group, Sep 2026)</t>
+          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20355,27 +20311,27 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-09</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Entity Contribution · projected EBITDA gap</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Repeat findings</t>
+          <t>Projected EBITDA gap · P07–P12</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>GOV-006</t>
+          <t>PRD-003</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -20385,16 +20341,16 @@
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>−9.2 ₹ m</t>
         </is>
       </c>
       <c r="I131" s="21">
-        <f>'Owner KPIs'!K95</f>
+        <f>'Owner KPIs'!K115</f>
         <v/>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 95 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20404,46 +20360,46 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Operations Impact · Plant 02 (Owner summary)</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Leadership KPIs affected by findings</t>
+          <t>Production vs plan · Plant 02 MTD</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>GOV-007</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100.2 % of plan</t>
         </is>
       </c>
       <c r="I132" s="21">
-        <f>'Owner KPIs'!K96</f>
+        <f>ROUND(IFERROR(100*'Plant Inputs'!N15/'Plant Inputs'!L15,0),2)</f>
         <v/>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 96 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20453,46 +20409,46 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Operations Impact · Plant 02 (Owner summary)</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Evidence completeness rate</t>
+          <t>Production at risk · Plant 02</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>GOV-008</t>
+          <t>SIG-007</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>18.4 kt (FCST)</t>
         </is>
       </c>
       <c r="I133" s="21">
-        <f>'Owner KPIs'!K98</f>
+        <f>ROUND('Plant Inputs'!AC15,2)</f>
         <v/>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 98 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20502,27 +20458,27 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Operations Impact · Plant 02 (Owner summary)</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>Average finding-closure time</t>
+          <t>Critical-material shortage risk · RM-1</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>GOV-009</t>
+          <t>SIG-009</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -20532,16 +20488,16 @@
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>34 d</t>
+          <t>3.5 days of cover</t>
         </is>
       </c>
       <c r="I134" s="21">
-        <f>'Owner KPIs'!K99</f>
+        <f>'Owner KPIs'!K15</f>
         <v/>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 99 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 15 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20551,46 +20507,46 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Operations Impact · Plant 02 (Owner summary)</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>KPI certification coverage</t>
+          <t>Days to breach · Plant 02 plan</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>TRU-001</t>
+          <t>PRD-001</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>84 % of leadership KPIs</t>
+          <t>4 days</t>
         </is>
       </c>
       <c r="I135" s="21">
-        <f>'Owner KPIs'!K100</f>
+        <f>ROUND('Plant Inputs'!BT15,2)</f>
         <v/>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 100 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20600,27 +20556,27 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-11</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Cash Exposure · how the supply issue reaches cash</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>Source-to-Lake reconciliation rate</t>
+          <t>Dispatch delays</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>TRU-008</t>
+          <t>SIG-012</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -20630,16 +20586,16 @@
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>2–4 days</t>
         </is>
       </c>
       <c r="I136" s="21">
-        <f>'Owner KPIs'!K102</f>
+        <f>'Owner KPIs'!K16</f>
         <v/>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 102 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 16 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20649,46 +20605,46 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-11</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Cash Exposure · how the supply issue reaches cash</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Flash-to-MIS reconciliation rate</t>
+          <t>Daily collections · A1</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>TRU-009</t>
+          <t>CSH-003</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Entity A1</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>4.1 ₹ m</t>
         </is>
       </c>
       <c r="I137" s="21">
-        <f>'Owner KPIs'!K103</f>
+        <f>ROUND('Entity Inputs'!CM9/'Entity Inputs'!D9/1000,2)</f>
         <v/>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 103 (Group, Sep 2026)</t>
+          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20698,27 +20654,27 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-11</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Cash Exposure · how the supply issue reaches cash</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>Flash-to-Close variance (P06)</t>
+          <t>Cash-upstream exposure</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>TRU-010</t>
+          <t>CSH-006</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -20728,16 +20684,16 @@
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>0.6 %</t>
+          <t>26 ₹ m</t>
         </is>
       </c>
       <c r="I138" s="21">
-        <f>'Owner KPIs'!K104</f>
+        <f>'Owner KPIs'!K40</f>
         <v/>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 104 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 40 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20747,46 +20703,46 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-11</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Cash Exposure · how the supply issue reaches cash</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Variance against Board numbers</t>
+          <t>DSO · Entity A1</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>TRU-011</t>
+          <t>WCP-001</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Entity A1</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>0.3% max abs · Entity B2</t>
+          <t>52 days</t>
         </is>
       </c>
       <c r="I139" s="21">
-        <f>'Owner KPIs'!K105</f>
+        <f>ROUND((IF('Entity Inputs'!AU9=0,0,'Entity Inputs'!CJ9/'Entity Inputs'!AU9*'Entity Inputs'!D9)),2)</f>
         <v/>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 105 (Group, Sep 2026)</t>
+          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20796,12 +20752,12 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>S-03 · Owner view</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>KPI Detail and Lineage · OPS-001 Production vs plan · Entity A1</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -20811,7 +20767,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Entity A1 MTD</t>
+          <t>Production vs plan · Group MTD</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -20821,21 +20777,21 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>Entity A1</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>103.2 % of plan (flash)</t>
+          <t>98.1 % of plan</t>
         </is>
       </c>
       <c r="I140" s="21">
-        <f>ROUND(IFERROR(100*'Entity Inputs'!M9/'Entity Inputs'!K9,0),2)</f>
+        <f>'Owner KPIs'!K2</f>
         <v/>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20845,12 +20801,12 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>S-09</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Entity Contribution · projected EBITDA gap</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -20860,12 +20816,12 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Projected EBITDA gap · P07–P12</t>
+          <t>EBITDA YTD (to P06)</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>PRD-003</t>
+          <t>FIN-001</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -20875,16 +20831,16 @@
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>−9.2 ₹ m</t>
+          <t>361.3 ₹ m</t>
         </is>
       </c>
       <c r="I141" s="21">
-        <f>'Owner KPIs'!K115</f>
+        <f>'Owner KPIs'!K29</f>
         <v/>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 29 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20894,12 +20850,12 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Operations Impact · Plant 02 (Owner summary)</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -20909,31 +20865,31 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Plant 02 MTD</t>
+          <t>Free Cash Flow YTD</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>FIN-004</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>100.2 % of plan</t>
+          <t>96.4 ₹ m</t>
         </is>
       </c>
       <c r="I142" s="21">
-        <f>ROUND(IFERROR(100*'Plant Inputs'!N15/'Plant Inputs'!L15,0),2)</f>
+        <f>'Owner KPIs'!K32</f>
         <v/>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 32 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20943,12 +20899,12 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Operations Impact · Plant 02 (Owner summary)</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -20958,31 +20914,31 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Production at risk · Plant 02</t>
+          <t>Net Debt</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>SIG-007</t>
+          <t>FIN-006</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>18.4 kt (FCST)</t>
+          <t>1,140 ₹ m</t>
         </is>
       </c>
       <c r="I143" s="21">
-        <f>ROUND('Plant Inputs'!AC15,2)</f>
+        <f>'Owner KPIs'!K34</f>
         <v/>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 34 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20992,12 +20948,12 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Operations Impact · Plant 02 (Owner summary)</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -21007,12 +20963,12 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Critical-material shortage risk · RM-1</t>
+          <t>Capex physical progress</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>SIG-009</t>
+          <t>CPX-004</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -21022,16 +20978,16 @@
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>3.5 days of cover</t>
+          <t>61 % weighted</t>
         </is>
       </c>
       <c r="I144" s="21">
-        <f>'Owner KPIs'!K15</f>
+        <f>'Owner KPIs'!K59</f>
         <v/>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 15 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 59 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21041,12 +20997,12 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Operations Impact · Plant 02 (Owner summary)</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -21056,31 +21012,31 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Days to breach · Plant 02 plan</t>
+          <t>Open critical alerts</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>PRD-001</t>
+          <t>EFF-002</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>4 days</t>
+          <t>1 alert</t>
         </is>
       </c>
       <c r="I145" s="21">
-        <f>ROUND('Plant Inputs'!BT15,2)</f>
+        <f>'Owner KPIs'!K106</f>
         <v/>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 106 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21090,46 +21046,46 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>S-11</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Cash Exposure · how the supply issue reaches cash</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Dispatch delays</t>
+          <t>Days to breach · Plant 02 plan</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>SIG-012</t>
+          <t>PRD-001</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>2–4 days</t>
+          <t>4 days</t>
         </is>
       </c>
       <c r="I146" s="21">
-        <f>'Owner KPIs'!K16</f>
+        <f>ROUND('Plant Inputs'!BT15,2)</f>
         <v/>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 16 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21139,46 +21095,46 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>S-11</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Cash Exposure · how the supply issue reaches cash</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Daily collections · A1</t>
+          <t>Probability of plan miss · P07</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>CSH-003</t>
+          <t>PRD-002</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>Entity A1</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>4.1 ₹ m</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I147" s="21">
-        <f>ROUND('Entity Inputs'!CM9/'Entity Inputs'!D9/1000,2)</f>
+        <f>'Owner KPIs'!K114</f>
         <v/>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 114 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21188,27 +21144,27 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>S-11</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Cash Exposure · how the supply issue reaches cash</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Cash-upstream exposure</t>
+          <t>Projected EBITDA gap · P07–P12</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>CSH-006</t>
+          <t>PRD-003</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -21218,16 +21174,16 @@
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>26 ₹ m</t>
+          <t>−₹9.2 m</t>
         </is>
       </c>
       <c r="I148" s="21">
-        <f>'Owner KPIs'!K40</f>
+        <f>'Owner KPIs'!K115</f>
         <v/>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 40 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21237,46 +21193,46 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>S-11</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Cash Exposure · how the supply issue reaches cash</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>DSO · Entity A1</t>
+          <t>Capacity utilization</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>WCP-001</t>
+          <t>OPS-003</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>Entity A1</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>52 days</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="I149" s="21">
-        <f>ROUND((IF('Entity Inputs'!AU9=0,0,'Entity Inputs'!CJ9/'Entity Inputs'!AU9*'Entity Inputs'!D9)),2)</f>
+        <f>'Owner KPIs'!K3</f>
         <v/>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21296,17 +21252,17 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Group MTD</t>
+          <t>Sales vs plan · MTD</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>OPS-002</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -21316,16 +21272,16 @@
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>98.1 % of plan</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="I150" s="21">
-        <f>'Owner KPIs'!K2</f>
+        <f>'Owner KPIs'!K26</f>
         <v/>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 26 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21345,17 +21301,17 @@
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>EBITDA YTD (to P06)</t>
+          <t>EBIT YTD</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>FIN-001</t>
+          <t>FIN-002</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -21365,16 +21321,16 @@
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>361.3 ₹ m</t>
+          <t>238.4 ₹ m</t>
         </is>
       </c>
       <c r="I151" s="21">
-        <f>'Owner KPIs'!K29</f>
+        <f>'Owner KPIs'!K30</f>
         <v/>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 29 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 30 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21394,17 +21350,17 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Free Cash Flow YTD</t>
+          <t>Revenue YTD</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>FIN-004</t>
+          <t>FIN-003</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -21414,16 +21370,16 @@
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>96.4 ₹ m</t>
+          <t>2,410 ₹ m</t>
         </is>
       </c>
       <c r="I152" s="21">
-        <f>'Owner KPIs'!K32</f>
+        <f>'Owner KPIs'!K31</f>
         <v/>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 32 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 31 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21443,17 +21399,17 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Net Debt</t>
+          <t>ROCE (rolling 12 m)</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>FIN-006</t>
+          <t>FIN-005</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -21463,16 +21419,16 @@
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>1,140 ₹ m</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="I153" s="21">
-        <f>'Owner KPIs'!K34</f>
+        <f>'Owner KPIs'!K33</f>
         <v/>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 34 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 33 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21492,17 +21448,17 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Capex physical progress</t>
+          <t>Shareholder-value indicator</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>CPX-004</t>
+          <t>FIN-007</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -21512,16 +21468,16 @@
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>61 % weighted</t>
+          <t>[PLACEHOLDER]</t>
         </is>
       </c>
       <c r="I154" s="21">
-        <f>'Owner KPIs'!K59</f>
+        <f>'Owner KPIs'!K35</f>
         <v/>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 59 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 35 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21541,17 +21497,17 @@
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Open critical alerts</t>
+          <t>Transformation progress</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>EFF-002</t>
+          <t>STR-002</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -21561,16 +21517,16 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>1 alert</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="I155" s="21">
-        <f>'Owner KPIs'!K106</f>
+        <f>'Owner KPIs'!K65</f>
         <v/>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 106 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 65 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21590,36 +21546,36 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Days to breach · Plant 02 plan</t>
+          <t>Regulatory breaches · YTD</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>PRD-001</t>
+          <t>RSK-003</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>4 days</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I156" s="21">
-        <f>ROUND('Plant Inputs'!BT15,2)</f>
+        <f>'Owner KPIs'!K79</f>
         <v/>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 79 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21629,7 +21585,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -21639,17 +21595,17 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Probability of plan miss · P07</t>
+          <t>Production vs plan · Group MTD</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>PRD-002</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -21659,16 +21615,16 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>98.1 % of plan</t>
         </is>
       </c>
       <c r="I157" s="21">
-        <f>'Owner KPIs'!K114</f>
+        <f>'Owner KPIs'!K2</f>
         <v/>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 114 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21678,7 +21634,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -21688,17 +21644,17 @@
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Projected EBITDA gap · P07–P12</t>
+          <t>EBITDA YTD (to P06)</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>PRD-003</t>
+          <t>FIN-001</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -21708,16 +21664,16 @@
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>−₹9.2 m</t>
+          <t>361.3 ₹ m</t>
         </is>
       </c>
       <c r="I158" s="21">
-        <f>'Owner KPIs'!K115</f>
+        <f>'Owner KPIs'!K29</f>
         <v/>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 29 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21727,7 +21683,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -21737,17 +21693,17 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Capacity utilization</t>
+          <t>Free Cash Flow YTD</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>OPS-003</t>
+          <t>FIN-004</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -21757,16 +21713,16 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>96.4 ₹ m</t>
         </is>
       </c>
       <c r="I159" s="21">
-        <f>'Owner KPIs'!K3</f>
+        <f>'Owner KPIs'!K32</f>
         <v/>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 32 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21776,7 +21732,7 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -21786,17 +21742,17 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Sales vs plan · MTD</t>
+          <t>Net Debt</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>OPS-002</t>
+          <t>FIN-006</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -21806,16 +21762,16 @@
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>1,140 ₹ m</t>
         </is>
       </c>
       <c r="I160" s="21">
-        <f>'Owner KPIs'!K26</f>
+        <f>'Owner KPIs'!K34</f>
         <v/>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 26 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 34 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21825,7 +21781,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -21835,17 +21791,17 @@
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>EBIT YTD</t>
+          <t>Capex physical progress</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>FIN-002</t>
+          <t>CPX-004</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -21855,16 +21811,16 @@
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>238.4 ₹ m</t>
+          <t>61 % weighted</t>
         </is>
       </c>
       <c r="I161" s="21">
-        <f>'Owner KPIs'!K30</f>
+        <f>'Owner KPIs'!K59</f>
         <v/>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 30 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 59 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21830,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -21884,17 +21840,17 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Revenue YTD</t>
+          <t>Open critical alerts</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>FIN-003</t>
+          <t>EFF-002</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -21904,16 +21860,16 @@
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>2,410 ₹ m</t>
+          <t>1 alert</t>
         </is>
       </c>
       <c r="I162" s="21">
-        <f>'Owner KPIs'!K31</f>
+        <f>'Owner KPIs'!K106</f>
         <v/>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 31 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 106 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21923,7 +21879,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -21933,36 +21889,36 @@
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>ROCE (rolling 12 m)</t>
+          <t>Days to breach · Plant 02 plan</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>FIN-005</t>
+          <t>PRD-001</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>4 days</t>
         </is>
       </c>
       <c r="I163" s="21">
-        <f>'Owner KPIs'!K33</f>
+        <f>ROUND('Plant Inputs'!BT15,2)</f>
         <v/>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 33 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21972,7 +21928,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -21982,17 +21938,17 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Shareholder-value indicator</t>
+          <t>Probability of plan miss · P07</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>FIN-007</t>
+          <t>PRD-002</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -22002,16 +21958,16 @@
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER]</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I164" s="21">
-        <f>'Owner KPIs'!K35</f>
+        <f>'Owner KPIs'!K114</f>
         <v/>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 35 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 114 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -22021,7 +21977,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -22031,17 +21987,17 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Transformation progress</t>
+          <t>Projected EBITDA gap · P07–P12</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>STR-002</t>
+          <t>PRD-003</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -22051,16 +22007,16 @@
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>−₹9.2 m</t>
         </is>
       </c>
       <c r="I165" s="21">
-        <f>'Owner KPIs'!K65</f>
+        <f>'Owner KPIs'!K115</f>
         <v/>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 65 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -22070,7 +22026,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -22085,12 +22041,12 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Regulatory breaches · YTD</t>
+          <t>Capacity utilization</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>RSK-003</t>
+          <t>OPS-003</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -22100,16 +22056,16 @@
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="I166" s="21">
-        <f>'Owner KPIs'!K79</f>
+        <f>'Owner KPIs'!K3</f>
         <v/>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 79 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -22129,17 +22085,17 @@
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Group MTD</t>
+          <t>Sales vs plan · MTD</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>OPS-002</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -22149,16 +22105,16 @@
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>98.1 % of plan</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="I167" s="21">
-        <f>'Owner KPIs'!K2</f>
+        <f>'Owner KPIs'!K26</f>
         <v/>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 26 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -22178,17 +22134,17 @@
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>EBITDA YTD (to P06)</t>
+          <t>EBIT YTD</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>FIN-001</t>
+          <t>FIN-002</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -22198,16 +22154,16 @@
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>361.3 ₹ m</t>
+          <t>238.4 ₹ m</t>
         </is>
       </c>
       <c r="I168" s="21">
-        <f>'Owner KPIs'!K29</f>
+        <f>'Owner KPIs'!K30</f>
         <v/>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 29 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 30 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -22227,17 +22183,17 @@
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Free Cash Flow YTD</t>
+          <t>Revenue YTD</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>FIN-004</t>
+          <t>FIN-003</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -22247,16 +22203,16 @@
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>96.4 ₹ m</t>
+          <t>2,410 ₹ m</t>
         </is>
       </c>
       <c r="I169" s="21">
-        <f>'Owner KPIs'!K32</f>
+        <f>'Owner KPIs'!K31</f>
         <v/>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 32 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 31 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -22276,17 +22232,17 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Net Debt</t>
+          <t>ROCE (rolling 12 m)</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>FIN-006</t>
+          <t>FIN-005</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -22296,16 +22252,16 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>1,140 ₹ m</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="I170" s="21">
-        <f>'Owner KPIs'!K34</f>
+        <f>'Owner KPIs'!K33</f>
         <v/>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 34 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 33 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -22325,17 +22281,17 @@
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Capex physical progress</t>
+          <t>Shareholder-value indicator</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>CPX-004</t>
+          <t>FIN-007</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -22345,16 +22301,16 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>61 % weighted</t>
+          <t>[PLACEHOLDER]</t>
         </is>
       </c>
       <c r="I171" s="21">
-        <f>'Owner KPIs'!K59</f>
+        <f>'Owner KPIs'!K35</f>
         <v/>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 59 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 35 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -22374,17 +22330,17 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Open critical alerts</t>
+          <t>Transformation progress</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>EFF-002</t>
+          <t>STR-002</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -22394,16 +22350,16 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>1 alert</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="I172" s="21">
-        <f>'Owner KPIs'!K106</f>
+        <f>'Owner KPIs'!K65</f>
         <v/>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 106 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 65 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -22423,531 +22379,41 @@
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Days to breach · Plant 02 plan</t>
+          <t>Regulatory breaches · YTD</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>PRD-001</t>
+          <t>RSK-003</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>4 days</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I173" s="21">
-        <f>ROUND('Plant Inputs'!BT15,2)</f>
+        <f>'Owner KPIs'!K79</f>
         <v/>
       </c>
       <c r="J173" s="3" t="inlineStr">
-        <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="n">
-        <v>173</v>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>Probability of plan miss · P07</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>PRD-002</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H174" s="3" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="I174" s="21">
-        <f>'Owner KPIs'!K114</f>
-        <v/>
-      </c>
-      <c r="J174" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 114 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>Projected EBITDA gap · P07–P12</t>
-        </is>
-      </c>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t>PRD-003</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H175" s="3" t="inlineStr">
-        <is>
-          <t>−₹9.2 m</t>
-        </is>
-      </c>
-      <c r="I175" s="21">
-        <f>'Owner KPIs'!K115</f>
-        <v/>
-      </c>
-      <c r="J175" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>Capacity utilization</t>
-        </is>
-      </c>
-      <c r="F176" s="3" t="inlineStr">
-        <is>
-          <t>OPS-003</t>
-        </is>
-      </c>
-      <c r="G176" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H176" s="3" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="I176" s="21">
-        <f>'Owner KPIs'!K3</f>
-        <v/>
-      </c>
-      <c r="J176" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>Sales vs plan · MTD</t>
-        </is>
-      </c>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t>OPS-002</t>
-        </is>
-      </c>
-      <c r="G177" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H177" s="3" t="inlineStr">
-        <is>
-          <t>97.6%</t>
-        </is>
-      </c>
-      <c r="I177" s="21">
-        <f>'Owner KPIs'!K26</f>
-        <v/>
-      </c>
-      <c r="J177" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 26 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="n">
-        <v>177</v>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>EBIT YTD</t>
-        </is>
-      </c>
-      <c r="F178" s="3" t="inlineStr">
-        <is>
-          <t>FIN-002</t>
-        </is>
-      </c>
-      <c r="G178" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H178" s="3" t="inlineStr">
-        <is>
-          <t>238.4 ₹ m</t>
-        </is>
-      </c>
-      <c r="I178" s="21">
-        <f>'Owner KPIs'!K30</f>
-        <v/>
-      </c>
-      <c r="J178" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 30 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="n">
-        <v>178</v>
-      </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>Revenue YTD</t>
-        </is>
-      </c>
-      <c r="F179" s="3" t="inlineStr">
-        <is>
-          <t>FIN-003</t>
-        </is>
-      </c>
-      <c r="G179" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H179" s="3" t="inlineStr">
-        <is>
-          <t>2,410 ₹ m</t>
-        </is>
-      </c>
-      <c r="I179" s="21">
-        <f>'Owner KPIs'!K31</f>
-        <v/>
-      </c>
-      <c r="J179" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 31 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="n">
-        <v>179</v>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>ROCE (rolling 12 m)</t>
-        </is>
-      </c>
-      <c r="F180" s="3" t="inlineStr">
-        <is>
-          <t>FIN-005</t>
-        </is>
-      </c>
-      <c r="G180" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H180" s="3" t="inlineStr">
-        <is>
-          <t>11.8%</t>
-        </is>
-      </c>
-      <c r="I180" s="21">
-        <f>'Owner KPIs'!K33</f>
-        <v/>
-      </c>
-      <c r="J180" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 33 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>Shareholder-value indicator</t>
-        </is>
-      </c>
-      <c r="F181" s="3" t="inlineStr">
-        <is>
-          <t>FIN-007</t>
-        </is>
-      </c>
-      <c r="G181" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H181" s="3" t="inlineStr">
-        <is>
-          <t>[PLACEHOLDER]</t>
-        </is>
-      </c>
-      <c r="I181" s="21">
-        <f>'Owner KPIs'!K35</f>
-        <v/>
-      </c>
-      <c r="J181" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 35 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="3" t="n">
-        <v>181</v>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="inlineStr">
-        <is>
-          <t>Transformation progress</t>
-        </is>
-      </c>
-      <c r="F182" s="3" t="inlineStr">
-        <is>
-          <t>STR-002</t>
-        </is>
-      </c>
-      <c r="G182" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H182" s="3" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="I182" s="21">
-        <f>'Owner KPIs'!K65</f>
-        <v/>
-      </c>
-      <c r="J182" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 65 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="n">
-        <v>182</v>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>Regulatory breaches · YTD</t>
-        </is>
-      </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>RSK-003</t>
-        </is>
-      </c>
-      <c r="G183" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H183" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I183" s="21">
-        <f>'Owner KPIs'!K79</f>
-        <v/>
-      </c>
-      <c r="J183" s="3" t="inlineStr">
         <is>
           <t>Owner KPIs sheet, row 79 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J183"/>
+  <autoFilter ref="A1:J173"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/kpi-model/Owner-KPI-Model.xlsx
+++ b/data/kpi-model/Owner-KPI-Model.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calculated vs Shown'!$A$1:$I$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Owner KPIs'!$A$1:$N$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Owner Screens'!$A$1:$J$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Owner Screens'!$A$1:$J$164</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Entity Inputs'!$A$3:$FU$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Plant Inputs'!$A$3:$BY$39</definedName>
   </definedNames>
@@ -738,7 +738,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>O-01, O-01 · large display ≥ 1600, O-09, STATE GALLERY · O-01 + S-02</t>
+          <t>O-01, O-01 · large display ≥ 1600, STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>7.8 h</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Different</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -912,17 +912,17 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>95.6 %</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Different</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>O-09, —</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>O-05, O-09</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -3810,17 +3810,17 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>91.4 %</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>Different</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>86% (O-01, STATE GALLERY); 83.4 % (O-09)</t>
+          <t>86% (O-01, STATE GALLERY)</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>O-01, O-01 · large display ≥ 1600, O-09, STATE GALLERY · O-01 + S-02</t>
+          <t>O-01, O-01 · large display ≥ 1600, STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>7.8 h (O-09)</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>95.6 % (O-09)</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -6629,12 +6629,12 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2,934 ₹/t (O-09)</t>
+          <t>Not on a screen; 2,934 ₹/t (O-09)</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>O-09, —</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>0.82 tCO2e/t (O-05); 427.7 kt CO2e (O-09)</t>
+          <t>0.82 tCO2e/t (O-05)</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>O-05, O-09</t>
+          <t>O-05</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -10721,12 +10721,12 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>91.4 % (O-09)</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -13981,7 +13981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J173"/>
+  <dimension ref="A1:J164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.7109375" customWidth="1" min="1" max="1"/>
@@ -18603,12 +18603,12 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Entity A1 (A1)</t>
+          <t>MTBF · Group</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>REL-001</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -18618,13 +18618,13 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>91.3 % of plan</t>
+          <t>270 h</t>
         </is>
       </c>
       <c r="I95" s="21" t="n"/>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 4 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18649,12 +18649,12 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Entity A2 (A2)</t>
+          <t>Cost per tonne · Group</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>CST-001</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -18664,13 +18664,13 @@
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>100.3 % of plan</t>
+          <t>2,934 ₹/t</t>
         </is>
       </c>
       <c r="I96" s="21" t="n"/>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 8 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18695,12 +18695,12 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Capacity utilisation</t>
+          <t>Power cost per tonne</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>OPS-003</t>
+          <t>CST-004</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -18710,13 +18710,13 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>83.4 %</t>
+          <t>174 ₹/t</t>
         </is>
       </c>
       <c r="I97" s="21" t="n"/>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 28 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18736,17 +18736,17 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>MTBF · Group</t>
+          <t>Production vs plan</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>REL-001</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -18756,13 +18756,17 @@
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>270 h</t>
-        </is>
-      </c>
-      <c r="I98" s="21" t="n"/>
+          <t>Apr–Sep monthly series</t>
+        </is>
+      </c>
+      <c r="I98" s="21" t="inlineStr">
+        <is>
+          <t>Apr–Sep: None, None, None, None, None, None</t>
+        </is>
+      </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 4 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 2 (Group, Apr–Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18782,12 +18786,12 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Mean time to repair</t>
+          <t>Reliability trend · mean time to repair</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -18802,13 +18806,17 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>7.8 h</t>
-        </is>
-      </c>
-      <c r="I99" s="21" t="n"/>
+          <t>Apr–Sep monthly series</t>
+        </is>
+      </c>
+      <c r="I99" s="21" t="inlineStr">
+        <is>
+          <t>Apr–Sep: None, None, None, None, None, None</t>
+        </is>
+      </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 5 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 5 (Group, Apr–Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18828,17 +18836,17 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Preventive-maintenance compliance</t>
+          <t>Sustainability curve · emissions</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>REL-005</t>
+          <t>SUS-002</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -18848,13 +18856,17 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>95.6 %</t>
-        </is>
-      </c>
-      <c r="I100" s="21" t="n"/>
+          <t>Apr–Sep monthly series</t>
+        </is>
+      </c>
+      <c r="I100" s="21" t="inlineStr">
+        <is>
+          <t>Apr–Sep: None, None, None, None, None, None</t>
+        </is>
+      </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 7 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 12 (Group, Apr–Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18864,12 +18876,12 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Operations Command View</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -18879,12 +18891,12 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Cost per tonne · Group</t>
+          <t>Leadership KPIs affected by findings</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>CST-001</t>
+          <t>GOV-007</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -18894,13 +18906,16 @@
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>2,934 ₹/t</t>
-        </is>
-      </c>
-      <c r="I101" s="21" t="n"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I101" s="21">
+        <f>'Owner KPIs'!K96</f>
+        <v/>
+      </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 8 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 96 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18910,12 +18925,12 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Operations Command View</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -18925,12 +18940,12 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Power cost per tonne</t>
+          <t>Material reconciliation breaks</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>CST-004</t>
+          <t>TRU-007</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -18940,13 +18955,16 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>174 ₹/t</t>
-        </is>
-      </c>
-      <c r="I102" s="21" t="n"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I102" s="21">
+        <f>'Owner KPIs'!K97</f>
+        <v/>
+      </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 28 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 97 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18956,12 +18974,12 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Operations Command View</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -18971,12 +18989,12 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>OEE</t>
+          <t>Certified KPI percentage</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>PLT-002</t>
+          <t>TRU-001</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -18986,11 +19004,18 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>84.1 %</t>
-        </is>
-      </c>
-      <c r="I103" s="21" t="n"/>
-      <c r="J103" s="3" t="inlineStr"/>
+          <t>84 % of leadership KPIs</t>
+        </is>
+      </c>
+      <c r="I103" s="21">
+        <f>'Owner KPIs'!K100</f>
+        <v/>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>Owner KPIs sheet, row 100 (Group, Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
@@ -18998,12 +19023,12 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Operations Command View</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -19013,12 +19038,12 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Supplier on-time delivery</t>
+          <t>Uncertified KPI count</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>SUP-001</t>
+          <t>TRU-002</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -19028,13 +19053,16 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>91.4 %</t>
-        </is>
-      </c>
-      <c r="I104" s="21" t="n"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I104" s="21">
+        <f>'Owner KPIs'!K101</f>
+        <v/>
+      </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 70 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 101 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19044,12 +19072,12 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Operations Command View</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -19059,12 +19087,12 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Supplier fill rate</t>
+          <t>Flash-to-Close variance (P06)</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>SUP-002</t>
+          <t>TRU-010</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -19074,11 +19102,18 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>96.8 %</t>
-        </is>
-      </c>
-      <c r="I105" s="21" t="n"/>
-      <c r="J105" s="3" t="inlineStr"/>
+          <t>0.6 %</t>
+        </is>
+      </c>
+      <c r="I105" s="21">
+        <f>'Owner KPIs'!K104</f>
+        <v/>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>Owner KPIs sheet, row 104 (Group, Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
@@ -19086,12 +19121,12 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Operations Command View</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -19101,12 +19136,12 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Emissions</t>
+          <t>Variance against Board numbers</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>SUS-002</t>
+          <t>TRU-011</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -19116,13 +19151,16 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>427.7 kt CO2e</t>
-        </is>
-      </c>
-      <c r="I106" s="21" t="n"/>
+          <t>0.3 % (max abs)</t>
+        </is>
+      </c>
+      <c r="I106" s="21">
+        <f>'Owner KPIs'!K105</f>
+        <v/>
+      </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 12 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 105 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19132,27 +19170,27 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Operations Command View</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Chart</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan</t>
+          <t>Ageing certification approvals</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>GOV-001</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -19162,17 +19200,16 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>Apr–Sep monthly series</t>
-        </is>
-      </c>
-      <c r="I107" s="21" t="inlineStr">
-        <is>
-          <t>Apr–Sep: None, None, None, None, None, None</t>
-        </is>
+          <t>2 &gt; [PH] d</t>
+        </is>
+      </c>
+      <c r="I107" s="21">
+        <f>'Owner KPIs'!K90</f>
+        <v/>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 2 (Group, Apr–Sep 2026)</t>
+          <t>Owner KPIs sheet, row 90 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19182,27 +19219,27 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Operations Command View</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Chart</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Reliability trend · mean time to repair</t>
+          <t>Override count (KPI)</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>REL-002</t>
+          <t>GOV-002</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -19212,17 +19249,16 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>Apr–Sep monthly series</t>
-        </is>
-      </c>
-      <c r="I108" s="21" t="inlineStr">
-        <is>
-          <t>Apr–Sep: None, None, None, None, None, None</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I108" s="21">
+        <f>'Owner KPIs'!K91</f>
+        <v/>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 5 (Group, Apr–Sep 2026)</t>
+          <t>Owner KPIs sheet, row 91 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19232,27 +19268,27 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Operations Command View</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Chart</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Sustainability curve · emissions</t>
+          <t>Recurring data-quality issues</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>SUS-002</t>
+          <t>GOV-003</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -19262,17 +19298,16 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>Apr–Sep monthly series</t>
-        </is>
-      </c>
-      <c r="I109" s="21" t="inlineStr">
-        <is>
-          <t>Apr–Sep: None, None, None, None, None, None</t>
-        </is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I109" s="21">
+        <f>'Owner KPIs'!K92</f>
+        <v/>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 12 (Group, Apr–Sep 2026)</t>
+          <t>Owner KPIs sheet, row 92 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19292,17 +19327,17 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Leadership KPIs affected by findings</t>
+          <t>Open audit findings</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>GOV-007</t>
+          <t>GOV-004</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -19312,16 +19347,16 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I110" s="21">
-        <f>'Owner KPIs'!K96</f>
+        <f>'Owner KPIs'!K93</f>
         <v/>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 96 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 93 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19341,17 +19376,17 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Material reconciliation breaks</t>
+          <t>Overdue assurance actions</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>TRU-007</t>
+          <t>GOV-005</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -19361,16 +19396,16 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I111" s="21">
-        <f>'Owner KPIs'!K97</f>
+        <f>'Owner KPIs'!K94</f>
         <v/>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 97 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 94 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19390,17 +19425,17 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Certified KPI percentage</t>
+          <t>Repeat findings</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>TRU-001</t>
+          <t>GOV-006</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -19410,16 +19445,16 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>84 % of leadership KPIs</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I112" s="21">
-        <f>'Owner KPIs'!K100</f>
+        <f>'Owner KPIs'!K95</f>
         <v/>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 100 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 95 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19439,17 +19474,17 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Uncertified KPI count</t>
+          <t>Leadership KPIs affected by findings</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>TRU-002</t>
+          <t>GOV-007</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -19459,16 +19494,16 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I113" s="21">
-        <f>'Owner KPIs'!K101</f>
+        <f>'Owner KPIs'!K96</f>
         <v/>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 101 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 96 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19488,17 +19523,17 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Flash-to-Close variance (P06)</t>
+          <t>Evidence completeness rate</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>TRU-010</t>
+          <t>GOV-008</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -19508,16 +19543,16 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>0.6 %</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="I114" s="21">
-        <f>'Owner KPIs'!K104</f>
+        <f>'Owner KPIs'!K98</f>
         <v/>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 104 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 98 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19537,17 +19572,17 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Variance against Board numbers</t>
+          <t>Average finding-closure time</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>TRU-011</t>
+          <t>GOV-009</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -19557,16 +19592,16 @@
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>0.3 % (max abs)</t>
+          <t>34 d</t>
         </is>
       </c>
       <c r="I115" s="21">
-        <f>'Owner KPIs'!K105</f>
+        <f>'Owner KPIs'!K99</f>
         <v/>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 105 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 99 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19591,12 +19626,12 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Ageing certification approvals</t>
+          <t>KPI certification coverage</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>GOV-001</t>
+          <t>TRU-001</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -19606,16 +19641,16 @@
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>2 &gt; [PH] d</t>
+          <t>84 % of leadership KPIs</t>
         </is>
       </c>
       <c r="I116" s="21">
-        <f>'Owner KPIs'!K90</f>
+        <f>'Owner KPIs'!K100</f>
         <v/>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 90 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 100 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19640,12 +19675,12 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Override count (KPI)</t>
+          <t>Source-to-Lake reconciliation rate</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>GOV-002</t>
+          <t>TRU-008</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -19655,16 +19690,16 @@
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="I117" s="21">
-        <f>'Owner KPIs'!K91</f>
+        <f>'Owner KPIs'!K102</f>
         <v/>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 91 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 102 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19689,12 +19724,12 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Recurring data-quality issues</t>
+          <t>Flash-to-MIS reconciliation rate</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>GOV-003</t>
+          <t>TRU-009</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -19704,16 +19739,16 @@
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="I118" s="21">
-        <f>'Owner KPIs'!K92</f>
+        <f>'Owner KPIs'!K103</f>
         <v/>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 92 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 103 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19738,12 +19773,12 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Open audit findings</t>
+          <t>Flash-to-Close variance (P06)</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>GOV-004</t>
+          <t>TRU-010</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -19753,16 +19788,16 @@
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0.6 %</t>
         </is>
       </c>
       <c r="I119" s="21">
-        <f>'Owner KPIs'!K93</f>
+        <f>'Owner KPIs'!K104</f>
         <v/>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 93 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 104 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19787,12 +19822,12 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Overdue assurance actions</t>
+          <t>Variance against Board numbers</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>GOV-005</t>
+          <t>TRU-011</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -19802,16 +19837,16 @@
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.3% max abs · Entity B2</t>
         </is>
       </c>
       <c r="I120" s="21">
-        <f>'Owner KPIs'!K94</f>
+        <f>'Owner KPIs'!K105</f>
         <v/>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 94 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 105 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19821,46 +19856,46 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-03 · Owner view</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>KPI Detail and Lineage · OPS-001 Production vs plan · Entity A1</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Repeat findings</t>
+          <t>Production vs plan · Entity A1 MTD</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>GOV-006</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Entity A1</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>103.2 % of plan (flash)</t>
         </is>
       </c>
       <c r="I121" s="21">
-        <f>'Owner KPIs'!K95</f>
+        <f>ROUND(IFERROR(100*'Entity Inputs'!M9/'Entity Inputs'!K9,0),2)</f>
         <v/>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 95 (Group, Sep 2026)</t>
+          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19870,27 +19905,27 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-09</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Entity Contribution · projected EBITDA gap</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Leadership KPIs affected by findings</t>
+          <t>Projected EBITDA gap · P07–P12</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>GOV-007</t>
+          <t>PRD-003</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -19900,16 +19935,16 @@
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>−9.2 ₹ m</t>
         </is>
       </c>
       <c r="I122" s="21">
-        <f>'Owner KPIs'!K96</f>
+        <f>'Owner KPIs'!K115</f>
         <v/>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 96 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19919,46 +19954,46 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Operations Impact · Plant 02 (Owner summary)</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Evidence completeness rate</t>
+          <t>Production vs plan · Plant 02 MTD</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>GOV-008</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>100.2 % of plan</t>
         </is>
       </c>
       <c r="I123" s="21">
-        <f>'Owner KPIs'!K98</f>
+        <f>ROUND(IFERROR(100*'Plant Inputs'!N15/'Plant Inputs'!L15,0),2)</f>
         <v/>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 98 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19968,46 +20003,46 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Operations Impact · Plant 02 (Owner summary)</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Average finding-closure time</t>
+          <t>Production at risk · Plant 02</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>GOV-009</t>
+          <t>SIG-007</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>34 d</t>
+          <t>18.4 kt (FCST)</t>
         </is>
       </c>
       <c r="I124" s="21">
-        <f>'Owner KPIs'!K99</f>
+        <f>ROUND('Plant Inputs'!AC15,2)</f>
         <v/>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 99 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20017,27 +20052,27 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Operations Impact · Plant 02 (Owner summary)</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>KPI certification coverage</t>
+          <t>Critical-material shortage risk · RM-1</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>TRU-001</t>
+          <t>SIG-009</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -20047,16 +20082,16 @@
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>84 % of leadership KPIs</t>
+          <t>3.5 days of cover</t>
         </is>
       </c>
       <c r="I125" s="21">
-        <f>'Owner KPIs'!K100</f>
+        <f>'Owner KPIs'!K15</f>
         <v/>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 100 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 15 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20066,46 +20101,46 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Operations Impact · Plant 02 (Owner summary)</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Source-to-Lake reconciliation rate</t>
+          <t>Days to breach · Plant 02 plan</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>TRU-008</t>
+          <t>PRD-001</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>4 days</t>
         </is>
       </c>
       <c r="I126" s="21">
-        <f>'Owner KPIs'!K102</f>
+        <f>ROUND('Plant Inputs'!BT15,2)</f>
         <v/>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 102 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20115,27 +20150,27 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-11</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Cash Exposure · how the supply issue reaches cash</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Flash-to-MIS reconciliation rate</t>
+          <t>Dispatch delays</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>TRU-009</t>
+          <t>SIG-012</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -20145,16 +20180,16 @@
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>2–4 days</t>
         </is>
       </c>
       <c r="I127" s="21">
-        <f>'Owner KPIs'!K103</f>
+        <f>'Owner KPIs'!K16</f>
         <v/>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 103 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 16 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20164,46 +20199,46 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-11</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Cash Exposure · how the supply issue reaches cash</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Flash-to-Close variance (P06)</t>
+          <t>Daily collections · A1</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>TRU-010</t>
+          <t>CSH-003</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Entity A1</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>0.6 %</t>
+          <t>4.1 ₹ m</t>
         </is>
       </c>
       <c r="I128" s="21">
-        <f>'Owner KPIs'!K104</f>
+        <f>ROUND('Entity Inputs'!CM9/'Entity Inputs'!D9/1000,2)</f>
         <v/>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 104 (Group, Sep 2026)</t>
+          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20213,27 +20248,27 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-11</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>Cash Exposure · how the supply issue reaches cash</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Variance against Board numbers</t>
+          <t>Cash-upstream exposure</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>TRU-011</t>
+          <t>CSH-006</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -20243,16 +20278,16 @@
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>0.3% max abs · Entity B2</t>
+          <t>26 ₹ m</t>
         </is>
       </c>
       <c r="I129" s="21">
-        <f>'Owner KPIs'!K105</f>
+        <f>'Owner KPIs'!K40</f>
         <v/>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 105 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 40 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20262,12 +20297,12 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>S-03 · Owner view</t>
+          <t>S-11</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>KPI Detail and Lineage · OPS-001 Production vs plan · Entity A1</t>
+          <t>Cash Exposure · how the supply issue reaches cash</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -20277,12 +20312,12 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Entity A1 MTD</t>
+          <t>DSO · Entity A1</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>WCP-001</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -20292,11 +20327,11 @@
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>103.2 % of plan (flash)</t>
+          <t>52 days</t>
         </is>
       </c>
       <c r="I130" s="21">
-        <f>ROUND(IFERROR(100*'Entity Inputs'!M9/'Entity Inputs'!K9,0),2)</f>
+        <f>ROUND((IF('Entity Inputs'!AU9=0,0,'Entity Inputs'!CJ9/'Entity Inputs'!AU9*'Entity Inputs'!D9)),2)</f>
         <v/>
       </c>
       <c r="J130" s="3" t="inlineStr">
@@ -20311,12 +20346,12 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>S-09</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Entity Contribution · projected EBITDA gap</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -20326,12 +20361,12 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Projected EBITDA gap · P07–P12</t>
+          <t>Production vs plan · Group MTD</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>PRD-003</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -20341,16 +20376,16 @@
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>−9.2 ₹ m</t>
+          <t>98.1 % of plan</t>
         </is>
       </c>
       <c r="I131" s="21">
-        <f>'Owner KPIs'!K115</f>
+        <f>'Owner KPIs'!K2</f>
         <v/>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20360,12 +20395,12 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Operations Impact · Plant 02 (Owner summary)</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
@@ -20375,31 +20410,31 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Plant 02 MTD</t>
+          <t>EBITDA YTD (to P06)</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>FIN-001</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>100.2 % of plan</t>
+          <t>361.3 ₹ m</t>
         </is>
       </c>
       <c r="I132" s="21">
-        <f>ROUND(IFERROR(100*'Plant Inputs'!N15/'Plant Inputs'!L15,0),2)</f>
+        <f>'Owner KPIs'!K29</f>
         <v/>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 29 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20409,12 +20444,12 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Operations Impact · Plant 02 (Owner summary)</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -20424,31 +20459,31 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Production at risk · Plant 02</t>
+          <t>Free Cash Flow YTD</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>SIG-007</t>
+          <t>FIN-004</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>18.4 kt (FCST)</t>
+          <t>96.4 ₹ m</t>
         </is>
       </c>
       <c r="I133" s="21">
-        <f>ROUND('Plant Inputs'!AC15,2)</f>
+        <f>'Owner KPIs'!K32</f>
         <v/>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 32 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20458,12 +20493,12 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Operations Impact · Plant 02 (Owner summary)</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -20473,12 +20508,12 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>Critical-material shortage risk · RM-1</t>
+          <t>Net Debt</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>SIG-009</t>
+          <t>FIN-006</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -20488,16 +20523,16 @@
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>3.5 days of cover</t>
+          <t>1,140 ₹ m</t>
         </is>
       </c>
       <c r="I134" s="21">
-        <f>'Owner KPIs'!K15</f>
+        <f>'Owner KPIs'!K34</f>
         <v/>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 15 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 34 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20507,12 +20542,12 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Operations Impact · Plant 02 (Owner summary)</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -20522,31 +20557,31 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Days to breach · Plant 02 plan</t>
+          <t>Capex physical progress</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>PRD-001</t>
+          <t>CPX-004</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>4 days</t>
+          <t>61 % weighted</t>
         </is>
       </c>
       <c r="I135" s="21">
-        <f>ROUND('Plant Inputs'!BT15,2)</f>
+        <f>'Owner KPIs'!K59</f>
         <v/>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 59 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20556,12 +20591,12 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>S-11</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Cash Exposure · how the supply issue reaches cash</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -20571,12 +20606,12 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>Dispatch delays</t>
+          <t>Open critical alerts</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>SIG-012</t>
+          <t>EFF-002</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -20586,16 +20621,16 @@
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>2–4 days</t>
+          <t>1 alert</t>
         </is>
       </c>
       <c r="I136" s="21">
-        <f>'Owner KPIs'!K16</f>
+        <f>'Owner KPIs'!K106</f>
         <v/>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 16 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 106 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20605,46 +20640,46 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>S-11</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Cash Exposure · how the supply issue reaches cash</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Daily collections · A1</t>
+          <t>Days to breach · Plant 02 plan</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>CSH-003</t>
+          <t>PRD-001</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>Entity A1</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>4.1 ₹ m</t>
+          <t>4 days</t>
         </is>
       </c>
       <c r="I137" s="21">
-        <f>ROUND('Entity Inputs'!CM9/'Entity Inputs'!D9/1000,2)</f>
+        <f>ROUND('Plant Inputs'!BT15,2)</f>
         <v/>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20654,27 +20689,27 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>S-11</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Cash Exposure · how the supply issue reaches cash</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>Cash-upstream exposure</t>
+          <t>Probability of plan miss · P07</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>CSH-006</t>
+          <t>PRD-002</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -20684,16 +20719,16 @@
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>26 ₹ m</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I138" s="21">
-        <f>'Owner KPIs'!K40</f>
+        <f>'Owner KPIs'!K114</f>
         <v/>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 40 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 114 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20703,46 +20738,46 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>S-11</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Cash Exposure · how the supply issue reaches cash</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>DSO · Entity A1</t>
+          <t>Projected EBITDA gap · P07–P12</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>WCP-001</t>
+          <t>PRD-003</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>Entity A1</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>52 days</t>
+          <t>−₹9.2 m</t>
         </is>
       </c>
       <c r="I139" s="21">
-        <f>ROUND((IF('Entity Inputs'!AU9=0,0,'Entity Inputs'!CJ9/'Entity Inputs'!AU9*'Entity Inputs'!D9)),2)</f>
+        <f>'Owner KPIs'!K115</f>
         <v/>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20762,17 +20797,17 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Group MTD</t>
+          <t>Capacity utilization</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>OPS-003</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -20782,16 +20817,16 @@
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>98.1 % of plan</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="I140" s="21">
-        <f>'Owner KPIs'!K2</f>
+        <f>'Owner KPIs'!K3</f>
         <v/>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20811,17 +20846,17 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>EBITDA YTD (to P06)</t>
+          <t>Sales vs plan · MTD</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>FIN-001</t>
+          <t>OPS-002</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -20831,16 +20866,16 @@
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>361.3 ₹ m</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="I141" s="21">
-        <f>'Owner KPIs'!K29</f>
+        <f>'Owner KPIs'!K26</f>
         <v/>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 29 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 26 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20860,17 +20895,17 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>Free Cash Flow YTD</t>
+          <t>EBIT YTD</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>FIN-004</t>
+          <t>FIN-002</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -20880,16 +20915,16 @@
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>96.4 ₹ m</t>
+          <t>238.4 ₹ m</t>
         </is>
       </c>
       <c r="I142" s="21">
-        <f>'Owner KPIs'!K32</f>
+        <f>'Owner KPIs'!K30</f>
         <v/>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 32 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 30 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20909,17 +20944,17 @@
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Net Debt</t>
+          <t>Revenue YTD</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>FIN-006</t>
+          <t>FIN-003</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -20929,16 +20964,16 @@
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>1,140 ₹ m</t>
+          <t>2,410 ₹ m</t>
         </is>
       </c>
       <c r="I143" s="21">
-        <f>'Owner KPIs'!K34</f>
+        <f>'Owner KPIs'!K31</f>
         <v/>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 34 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 31 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20958,17 +20993,17 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Capex physical progress</t>
+          <t>ROCE (rolling 12 m)</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>CPX-004</t>
+          <t>FIN-005</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -20978,16 +21013,16 @@
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>61 % weighted</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="I144" s="21">
-        <f>'Owner KPIs'!K59</f>
+        <f>'Owner KPIs'!K33</f>
         <v/>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 59 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 33 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21007,17 +21042,17 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Open critical alerts</t>
+          <t>Shareholder-value indicator</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>EFF-002</t>
+          <t>FIN-007</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -21027,16 +21062,16 @@
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>1 alert</t>
+          <t>[PLACEHOLDER]</t>
         </is>
       </c>
       <c r="I145" s="21">
-        <f>'Owner KPIs'!K106</f>
+        <f>'Owner KPIs'!K35</f>
         <v/>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 106 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 35 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21056,36 +21091,36 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Days to breach · Plant 02 plan</t>
+          <t>Transformation progress</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>PRD-001</t>
+          <t>STR-002</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>4 days</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="I146" s="21">
-        <f>ROUND('Plant Inputs'!BT15,2)</f>
+        <f>'Owner KPIs'!K65</f>
         <v/>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 65 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21105,17 +21140,17 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Probability of plan miss · P07</t>
+          <t>Regulatory breaches · YTD</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>PRD-002</t>
+          <t>RSK-003</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -21125,16 +21160,16 @@
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I147" s="21">
-        <f>'Owner KPIs'!K114</f>
+        <f>'Owner KPIs'!K79</f>
         <v/>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 114 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 79 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21144,7 +21179,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -21154,17 +21189,17 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Projected EBITDA gap · P07–P12</t>
+          <t>Production vs plan · Group MTD</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>PRD-003</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -21174,16 +21209,16 @@
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>−₹9.2 m</t>
+          <t>98.1 % of plan</t>
         </is>
       </c>
       <c r="I148" s="21">
-        <f>'Owner KPIs'!K115</f>
+        <f>'Owner KPIs'!K2</f>
         <v/>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21193,7 +21228,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -21203,17 +21238,17 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Capacity utilization</t>
+          <t>EBITDA YTD (to P06)</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>OPS-003</t>
+          <t>FIN-001</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -21223,16 +21258,16 @@
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>361.3 ₹ m</t>
         </is>
       </c>
       <c r="I149" s="21">
-        <f>'Owner KPIs'!K3</f>
+        <f>'Owner KPIs'!K29</f>
         <v/>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 29 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21242,7 +21277,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -21252,17 +21287,17 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Sales vs plan · MTD</t>
+          <t>Free Cash Flow YTD</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>OPS-002</t>
+          <t>FIN-004</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -21272,16 +21307,16 @@
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>96.4 ₹ m</t>
         </is>
       </c>
       <c r="I150" s="21">
-        <f>'Owner KPIs'!K26</f>
+        <f>'Owner KPIs'!K32</f>
         <v/>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 26 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 32 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21291,7 +21326,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -21301,17 +21336,17 @@
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>EBIT YTD</t>
+          <t>Net Debt</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>FIN-002</t>
+          <t>FIN-006</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -21321,16 +21356,16 @@
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>238.4 ₹ m</t>
+          <t>1,140 ₹ m</t>
         </is>
       </c>
       <c r="I151" s="21">
-        <f>'Owner KPIs'!K30</f>
+        <f>'Owner KPIs'!K34</f>
         <v/>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 30 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 34 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21340,7 +21375,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -21350,17 +21385,17 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Revenue YTD</t>
+          <t>Capex physical progress</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>FIN-003</t>
+          <t>CPX-004</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -21370,16 +21405,16 @@
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>2,410 ₹ m</t>
+          <t>61 % weighted</t>
         </is>
       </c>
       <c r="I152" s="21">
-        <f>'Owner KPIs'!K31</f>
+        <f>'Owner KPIs'!K59</f>
         <v/>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 31 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 59 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21389,7 +21424,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -21399,17 +21434,17 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>ROCE (rolling 12 m)</t>
+          <t>Open critical alerts</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>FIN-005</t>
+          <t>EFF-002</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -21419,16 +21454,16 @@
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>1 alert</t>
         </is>
       </c>
       <c r="I153" s="21">
-        <f>'Owner KPIs'!K33</f>
+        <f>'Owner KPIs'!K106</f>
         <v/>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 33 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 106 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21438,7 +21473,7 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -21448,36 +21483,36 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Shareholder-value indicator</t>
+          <t>Days to breach · Plant 02 plan</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>FIN-007</t>
+          <t>PRD-001</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER]</t>
+          <t>4 days</t>
         </is>
       </c>
       <c r="I154" s="21">
-        <f>'Owner KPIs'!K35</f>
+        <f>ROUND('Plant Inputs'!BT15,2)</f>
         <v/>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 35 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21487,7 +21522,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -21497,17 +21532,17 @@
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Transformation progress</t>
+          <t>Probability of plan miss · P07</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>STR-002</t>
+          <t>PRD-002</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -21517,16 +21552,16 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I155" s="21">
-        <f>'Owner KPIs'!K65</f>
+        <f>'Owner KPIs'!K114</f>
         <v/>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 65 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 114 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21571,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -21546,17 +21581,17 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Regulatory breaches · YTD</t>
+          <t>Projected EBITDA gap · P07–P12</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>RSK-003</t>
+          <t>PRD-003</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -21566,16 +21601,16 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>−₹9.2 m</t>
         </is>
       </c>
       <c r="I156" s="21">
-        <f>'Owner KPIs'!K79</f>
+        <f>'Owner KPIs'!K115</f>
         <v/>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 79 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21595,17 +21630,17 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Group MTD</t>
+          <t>Capacity utilization</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>OPS-003</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -21615,16 +21650,16 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>98.1 % of plan</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="I157" s="21">
-        <f>'Owner KPIs'!K2</f>
+        <f>'Owner KPIs'!K3</f>
         <v/>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21644,17 +21679,17 @@
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>EBITDA YTD (to P06)</t>
+          <t>Sales vs plan · MTD</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>FIN-001</t>
+          <t>OPS-002</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -21664,16 +21699,16 @@
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>361.3 ₹ m</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="I158" s="21">
-        <f>'Owner KPIs'!K29</f>
+        <f>'Owner KPIs'!K26</f>
         <v/>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 29 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 26 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21693,17 +21728,17 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Free Cash Flow YTD</t>
+          <t>EBIT YTD</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>FIN-004</t>
+          <t>FIN-002</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -21713,16 +21748,16 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>96.4 ₹ m</t>
+          <t>238.4 ₹ m</t>
         </is>
       </c>
       <c r="I159" s="21">
-        <f>'Owner KPIs'!K32</f>
+        <f>'Owner KPIs'!K30</f>
         <v/>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 32 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 30 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21742,17 +21777,17 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Net Debt</t>
+          <t>Revenue YTD</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>FIN-006</t>
+          <t>FIN-003</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -21762,16 +21797,16 @@
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>1,140 ₹ m</t>
+          <t>2,410 ₹ m</t>
         </is>
       </c>
       <c r="I160" s="21">
-        <f>'Owner KPIs'!K34</f>
+        <f>'Owner KPIs'!K31</f>
         <v/>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 34 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 31 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21791,17 +21826,17 @@
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Capex physical progress</t>
+          <t>ROCE (rolling 12 m)</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>CPX-004</t>
+          <t>FIN-005</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -21811,16 +21846,16 @@
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>61 % weighted</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="I161" s="21">
-        <f>'Owner KPIs'!K59</f>
+        <f>'Owner KPIs'!K33</f>
         <v/>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 59 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 33 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21840,17 +21875,17 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Open critical alerts</t>
+          <t>Shareholder-value indicator</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>EFF-002</t>
+          <t>FIN-007</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -21860,16 +21895,16 @@
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>1 alert</t>
+          <t>[PLACEHOLDER]</t>
         </is>
       </c>
       <c r="I162" s="21">
-        <f>'Owner KPIs'!K106</f>
+        <f>'Owner KPIs'!K35</f>
         <v/>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 106 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 35 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21889,36 +21924,36 @@
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Days to breach · Plant 02 plan</t>
+          <t>Transformation progress</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>PRD-001</t>
+          <t>STR-002</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>4 days</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="I163" s="21">
-        <f>ROUND('Plant Inputs'!BT15,2)</f>
+        <f>'Owner KPIs'!K65</f>
         <v/>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 65 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21938,17 +21973,17 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Probability of plan miss · P07</t>
+          <t>Regulatory breaches · YTD</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>PRD-002</t>
+          <t>RSK-003</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -21958,462 +21993,21 @@
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I164" s="21">
-        <f>'Owner KPIs'!K114</f>
+        <f>'Owner KPIs'!K79</f>
         <v/>
       </c>
       <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 114 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="n">
-        <v>164</v>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Tile</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>Projected EBITDA gap · P07–P12</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>PRD-003</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>−₹9.2 m</t>
-        </is>
-      </c>
-      <c r="I165" s="21">
-        <f>'Owner KPIs'!K115</f>
-        <v/>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="n">
-        <v>165</v>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>Capacity utilization</t>
-        </is>
-      </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>OPS-003</t>
-        </is>
-      </c>
-      <c r="G166" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="I166" s="21">
-        <f>'Owner KPIs'!K3</f>
-        <v/>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>Sales vs plan · MTD</t>
-        </is>
-      </c>
-      <c r="F167" s="3" t="inlineStr">
-        <is>
-          <t>OPS-002</t>
-        </is>
-      </c>
-      <c r="G167" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>97.6%</t>
-        </is>
-      </c>
-      <c r="I167" s="21">
-        <f>'Owner KPIs'!K26</f>
-        <v/>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 26 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>EBIT YTD</t>
-        </is>
-      </c>
-      <c r="F168" s="3" t="inlineStr">
-        <is>
-          <t>FIN-002</t>
-        </is>
-      </c>
-      <c r="G168" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>238.4 ₹ m</t>
-        </is>
-      </c>
-      <c r="I168" s="21">
-        <f>'Owner KPIs'!K30</f>
-        <v/>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 30 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="inlineStr">
-        <is>
-          <t>Revenue YTD</t>
-        </is>
-      </c>
-      <c r="F169" s="3" t="inlineStr">
-        <is>
-          <t>FIN-003</t>
-        </is>
-      </c>
-      <c r="G169" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>2,410 ₹ m</t>
-        </is>
-      </c>
-      <c r="I169" s="21">
-        <f>'Owner KPIs'!K31</f>
-        <v/>
-      </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 31 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="n">
-        <v>169</v>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>ROCE (rolling 12 m)</t>
-        </is>
-      </c>
-      <c r="F170" s="3" t="inlineStr">
-        <is>
-          <t>FIN-005</t>
-        </is>
-      </c>
-      <c r="G170" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H170" s="3" t="inlineStr">
-        <is>
-          <t>11.8%</t>
-        </is>
-      </c>
-      <c r="I170" s="21">
-        <f>'Owner KPIs'!K33</f>
-        <v/>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 33 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>Shareholder-value indicator</t>
-        </is>
-      </c>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t>FIN-007</t>
-        </is>
-      </c>
-      <c r="G171" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>[PLACEHOLDER]</t>
-        </is>
-      </c>
-      <c r="I171" s="21">
-        <f>'Owner KPIs'!K35</f>
-        <v/>
-      </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 35 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>Transformation progress</t>
-        </is>
-      </c>
-      <c r="F172" s="3" t="inlineStr">
-        <is>
-          <t>STR-002</t>
-        </is>
-      </c>
-      <c r="G172" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H172" s="3" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="I172" s="21">
-        <f>'Owner KPIs'!K65</f>
-        <v/>
-      </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 65 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>Regulatory breaches · YTD</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>RSK-003</t>
-        </is>
-      </c>
-      <c r="G173" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I173" s="21">
-        <f>'Owner KPIs'!K79</f>
-        <v/>
-      </c>
-      <c r="J173" s="3" t="inlineStr">
         <is>
           <t>Owner KPIs sheet, row 79 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J173"/>
+  <autoFilter ref="A1:J164"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/kpi-model/Owner-KPI-Model.xlsx
+++ b/data/kpi-model/Owner-KPI-Model.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calculated vs Shown'!$A$1:$I$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Owner KPIs'!$A$1:$N$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Owner Screens'!$A$1:$J$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Owner Screens'!$A$1:$J$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Entity Inputs'!$A$3:$FU$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Plant Inputs'!$A$3:$BY$39</definedName>
   </definedNames>
@@ -1878,17 +1878,17 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>174 ₹/t</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Different</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>174 ₹/t (O-09)</t>
+          <t>Not on a screen</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -13981,7 +13981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:J163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.7109375" customWidth="1" min="1" max="1"/>
@@ -18690,17 +18690,17 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Power cost per tonne</t>
+          <t>Production vs plan</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>CST-004</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -18710,13 +18710,17 @@
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>174 ₹/t</t>
-        </is>
-      </c>
-      <c r="I97" s="21" t="n"/>
+          <t>Apr–Sep monthly series</t>
+        </is>
+      </c>
+      <c r="I97" s="21" t="inlineStr">
+        <is>
+          <t>Apr–Sep: None, None, None, None, None, None</t>
+        </is>
+      </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 28 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 2 (Group, Apr–Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18741,12 +18745,12 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan</t>
+          <t>Reliability trend · mean time to repair</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>REL-002</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -18766,7 +18770,7 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 2 (Group, Apr–Sep 2026)</t>
+          <t>Owner KPIs sheet, row 5 (Group, Apr–Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18791,12 +18795,12 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Reliability trend · mean time to repair</t>
+          <t>Sustainability curve · emissions</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>REL-002</t>
+          <t>SUS-002</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -18816,7 +18820,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 5 (Group, Apr–Sep 2026)</t>
+          <t>Owner KPIs sheet, row 12 (Group, Apr–Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18826,27 +18830,27 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>O-09</t>
+          <t>G-08 · Owner depth</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Operations Command View</t>
+          <t>Trust Summary (Owner depth)</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Chart</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Sustainability curve · emissions</t>
+          <t>Leadership KPIs affected by findings</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>SUS-002</t>
+          <t>GOV-007</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -18856,17 +18860,16 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>Apr–Sep monthly series</t>
-        </is>
-      </c>
-      <c r="I100" s="21" t="inlineStr">
-        <is>
-          <t>Apr–Sep: None, None, None, None, None, None</t>
-        </is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I100" s="21">
+        <f>'Owner KPIs'!K96</f>
+        <v/>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 12 (Group, Apr–Sep 2026)</t>
+          <t>Owner KPIs sheet, row 96 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18891,12 +18894,12 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Leadership KPIs affected by findings</t>
+          <t>Material reconciliation breaks</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>GOV-007</t>
+          <t>TRU-007</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -18910,12 +18913,12 @@
         </is>
       </c>
       <c r="I101" s="21">
-        <f>'Owner KPIs'!K96</f>
+        <f>'Owner KPIs'!K97</f>
         <v/>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 96 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 97 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18940,12 +18943,12 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Material reconciliation breaks</t>
+          <t>Certified KPI percentage</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>TRU-007</t>
+          <t>TRU-001</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -18955,16 +18958,16 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>84 % of leadership KPIs</t>
         </is>
       </c>
       <c r="I102" s="21">
-        <f>'Owner KPIs'!K97</f>
+        <f>'Owner KPIs'!K100</f>
         <v/>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 97 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 100 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -18989,12 +18992,12 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Certified KPI percentage</t>
+          <t>Uncertified KPI count</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>TRU-001</t>
+          <t>TRU-002</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -19004,16 +19007,16 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>84 % of leadership KPIs</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I103" s="21">
-        <f>'Owner KPIs'!K100</f>
+        <f>'Owner KPIs'!K101</f>
         <v/>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 100 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 101 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19038,12 +19041,12 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Uncertified KPI count</t>
+          <t>Flash-to-Close variance (P06)</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>TRU-002</t>
+          <t>TRU-010</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -19053,16 +19056,16 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0.6 %</t>
         </is>
       </c>
       <c r="I104" s="21">
-        <f>'Owner KPIs'!K101</f>
+        <f>'Owner KPIs'!K104</f>
         <v/>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 101 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 104 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19087,12 +19090,12 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Flash-to-Close variance (P06)</t>
+          <t>Variance against Board numbers</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>TRU-010</t>
+          <t>TRU-011</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -19102,16 +19105,16 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>0.6 %</t>
+          <t>0.3 % (max abs)</t>
         </is>
       </c>
       <c r="I105" s="21">
-        <f>'Owner KPIs'!K104</f>
+        <f>'Owner KPIs'!K105</f>
         <v/>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 104 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 105 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19131,17 +19134,17 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Variance against Board numbers</t>
+          <t>Ageing certification approvals</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>TRU-011</t>
+          <t>GOV-001</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -19151,16 +19154,16 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>0.3 % (max abs)</t>
+          <t>2 &gt; [PH] d</t>
         </is>
       </c>
       <c r="I106" s="21">
-        <f>'Owner KPIs'!K105</f>
+        <f>'Owner KPIs'!K90</f>
         <v/>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 105 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 90 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19185,12 +19188,12 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Ageing certification approvals</t>
+          <t>Override count (KPI)</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>GOV-001</t>
+          <t>GOV-002</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -19200,16 +19203,16 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>2 &gt; [PH] d</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I107" s="21">
-        <f>'Owner KPIs'!K90</f>
+        <f>'Owner KPIs'!K91</f>
         <v/>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 90 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 91 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19234,12 +19237,12 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Override count (KPI)</t>
+          <t>Recurring data-quality issues</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>GOV-002</t>
+          <t>GOV-003</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -19249,16 +19252,16 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I108" s="21">
-        <f>'Owner KPIs'!K91</f>
+        <f>'Owner KPIs'!K92</f>
         <v/>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 91 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 92 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19283,12 +19286,12 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>Recurring data-quality issues</t>
+          <t>Open audit findings</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>GOV-003</t>
+          <t>GOV-004</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -19298,16 +19301,16 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I109" s="21">
-        <f>'Owner KPIs'!K92</f>
+        <f>'Owner KPIs'!K93</f>
         <v/>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 92 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 93 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19332,12 +19335,12 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Open audit findings</t>
+          <t>Overdue assurance actions</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>GOV-004</t>
+          <t>GOV-005</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -19347,16 +19350,16 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I110" s="21">
-        <f>'Owner KPIs'!K93</f>
+        <f>'Owner KPIs'!K94</f>
         <v/>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 93 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 94 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19381,12 +19384,12 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Overdue assurance actions</t>
+          <t>Repeat findings</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>GOV-005</t>
+          <t>GOV-006</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -19396,16 +19399,16 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I111" s="21">
-        <f>'Owner KPIs'!K94</f>
+        <f>'Owner KPIs'!K95</f>
         <v/>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 94 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 95 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19430,12 +19433,12 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Repeat findings</t>
+          <t>Leadership KPIs affected by findings</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>GOV-006</t>
+          <t>GOV-007</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -19449,12 +19452,12 @@
         </is>
       </c>
       <c r="I112" s="21">
-        <f>'Owner KPIs'!K95</f>
+        <f>'Owner KPIs'!K96</f>
         <v/>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 95 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 96 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19479,12 +19482,12 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>Leadership KPIs affected by findings</t>
+          <t>Evidence completeness rate</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>GOV-007</t>
+          <t>GOV-008</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -19494,16 +19497,16 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="I113" s="21">
-        <f>'Owner KPIs'!K96</f>
+        <f>'Owner KPIs'!K98</f>
         <v/>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 96 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 98 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19528,12 +19531,12 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Evidence completeness rate</t>
+          <t>Average finding-closure time</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>GOV-008</t>
+          <t>GOV-009</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -19543,16 +19546,16 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>34 d</t>
         </is>
       </c>
       <c r="I114" s="21">
-        <f>'Owner KPIs'!K98</f>
+        <f>'Owner KPIs'!K99</f>
         <v/>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 98 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 99 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19577,12 +19580,12 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Average finding-closure time</t>
+          <t>KPI certification coverage</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>GOV-009</t>
+          <t>TRU-001</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -19592,16 +19595,16 @@
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>34 d</t>
+          <t>84 % of leadership KPIs</t>
         </is>
       </c>
       <c r="I115" s="21">
-        <f>'Owner KPIs'!K99</f>
+        <f>'Owner KPIs'!K100</f>
         <v/>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 99 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 100 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19626,12 +19629,12 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>KPI certification coverage</t>
+          <t>Source-to-Lake reconciliation rate</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>TRU-001</t>
+          <t>TRU-008</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
@@ -19641,16 +19644,16 @@
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>84 % of leadership KPIs</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="I116" s="21">
-        <f>'Owner KPIs'!K100</f>
+        <f>'Owner KPIs'!K102</f>
         <v/>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 100 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 102 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19675,12 +19678,12 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Source-to-Lake reconciliation rate</t>
+          <t>Flash-to-MIS reconciliation rate</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>TRU-008</t>
+          <t>TRU-009</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -19690,16 +19693,16 @@
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="I117" s="21">
-        <f>'Owner KPIs'!K102</f>
+        <f>'Owner KPIs'!K103</f>
         <v/>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 102 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 103 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19724,12 +19727,12 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Flash-to-MIS reconciliation rate</t>
+          <t>Flash-to-Close variance (P06)</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>TRU-009</t>
+          <t>TRU-010</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -19739,16 +19742,16 @@
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>0.6 %</t>
         </is>
       </c>
       <c r="I118" s="21">
-        <f>'Owner KPIs'!K103</f>
+        <f>'Owner KPIs'!K104</f>
         <v/>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 103 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 104 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19773,12 +19776,12 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Flash-to-Close variance (P06)</t>
+          <t>Variance against Board numbers</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>TRU-010</t>
+          <t>TRU-011</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -19788,16 +19791,16 @@
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>0.6 %</t>
+          <t>0.3% max abs · Entity B2</t>
         </is>
       </c>
       <c r="I119" s="21">
-        <f>'Owner KPIs'!K104</f>
+        <f>'Owner KPIs'!K105</f>
         <v/>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 104 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 105 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19807,46 +19810,46 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>G-08 · Owner depth</t>
+          <t>S-03 · Owner view</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Trust Summary (Owner depth)</t>
+          <t>KPI Detail and Lineage · OPS-001 Production vs plan · Entity A1</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Variance against Board numbers</t>
+          <t>Production vs plan · Entity A1 MTD</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>TRU-011</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Entity A1</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>0.3% max abs · Entity B2</t>
+          <t>103.2 % of plan (flash)</t>
         </is>
       </c>
       <c r="I120" s="21">
-        <f>'Owner KPIs'!K105</f>
+        <f>ROUND(IFERROR(100*'Entity Inputs'!M9/'Entity Inputs'!K9,0),2)</f>
         <v/>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 105 (Group, Sep 2026)</t>
+          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19856,12 +19859,12 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>S-03 · Owner view</t>
+          <t>S-09</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>KPI Detail and Lineage · OPS-001 Production vs plan · Entity A1</t>
+          <t>Entity Contribution · projected EBITDA gap</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -19871,31 +19874,31 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Entity A1 MTD</t>
+          <t>Projected EBITDA gap · P07–P12</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>PRD-003</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>Entity A1</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>103.2 % of plan (flash)</t>
+          <t>−9.2 ₹ m</t>
         </is>
       </c>
       <c r="I121" s="21">
-        <f>ROUND(IFERROR(100*'Entity Inputs'!M9/'Entity Inputs'!K9,0),2)</f>
+        <f>'Owner KPIs'!K115</f>
         <v/>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19905,12 +19908,12 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>S-09</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Entity Contribution · projected EBITDA gap</t>
+          <t>Operations Impact · Plant 02 (Owner summary)</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -19920,31 +19923,31 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Projected EBITDA gap · P07–P12</t>
+          <t>Production vs plan · Plant 02 MTD</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>PRD-003</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>−9.2 ₹ m</t>
+          <t>100.2 % of plan</t>
         </is>
       </c>
       <c r="I122" s="21">
-        <f>'Owner KPIs'!K115</f>
+        <f>ROUND(IFERROR(100*'Plant Inputs'!N15/'Plant Inputs'!L15,0),2)</f>
         <v/>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -19969,12 +19972,12 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Plant 02 MTD</t>
+          <t>Production at risk · Plant 02</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>SIG-007</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -19984,11 +19987,11 @@
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>100.2 % of plan</t>
+          <t>18.4 kt (FCST)</t>
         </is>
       </c>
       <c r="I123" s="21">
-        <f>ROUND(IFERROR(100*'Plant Inputs'!N15/'Plant Inputs'!L15,0),2)</f>
+        <f>ROUND('Plant Inputs'!AC15,2)</f>
         <v/>
       </c>
       <c r="J123" s="3" t="inlineStr">
@@ -20018,31 +20021,31 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Production at risk · Plant 02</t>
+          <t>Critical-material shortage risk · RM-1</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>SIG-007</t>
+          <t>SIG-009</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>18.4 kt (FCST)</t>
+          <t>3.5 days of cover</t>
         </is>
       </c>
       <c r="I124" s="21">
-        <f>ROUND('Plant Inputs'!AC15,2)</f>
+        <f>'Owner KPIs'!K15</f>
         <v/>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 15 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20067,31 +20070,31 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Critical-material shortage risk · RM-1</t>
+          <t>Days to breach · Plant 02 plan</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>SIG-009</t>
+          <t>PRD-001</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>3.5 days of cover</t>
+          <t>4 days</t>
         </is>
       </c>
       <c r="I125" s="21">
-        <f>'Owner KPIs'!K15</f>
+        <f>ROUND('Plant Inputs'!BT15,2)</f>
         <v/>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 15 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20101,12 +20104,12 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>S-11</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Operations Impact · Plant 02 (Owner summary)</t>
+          <t>Cash Exposure · how the supply issue reaches cash</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -20116,31 +20119,31 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Days to breach · Plant 02 plan</t>
+          <t>Dispatch delays</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>PRD-001</t>
+          <t>SIG-012</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>4 days</t>
+          <t>2–4 days</t>
         </is>
       </c>
       <c r="I126" s="21">
-        <f>ROUND('Plant Inputs'!BT15,2)</f>
+        <f>'Owner KPIs'!K16</f>
         <v/>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 16 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20165,31 +20168,31 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Dispatch delays</t>
+          <t>Daily collections · A1</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>SIG-012</t>
+          <t>CSH-003</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Entity A1</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>2–4 days</t>
+          <t>4.1 ₹ m</t>
         </is>
       </c>
       <c r="I127" s="21">
-        <f>'Owner KPIs'!K16</f>
+        <f>ROUND('Entity Inputs'!CM9/'Entity Inputs'!D9/1000,2)</f>
         <v/>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 16 (Group, Sep 2026)</t>
+          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20214,31 +20217,31 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Daily collections · A1</t>
+          <t>Cash-upstream exposure</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>CSH-003</t>
+          <t>CSH-006</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>Entity A1</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>4.1 ₹ m</t>
+          <t>26 ₹ m</t>
         </is>
       </c>
       <c r="I128" s="21">
-        <f>ROUND('Entity Inputs'!CM9/'Entity Inputs'!D9/1000,2)</f>
+        <f>'Owner KPIs'!K40</f>
         <v/>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 40 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20263,31 +20266,31 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Cash-upstream exposure</t>
+          <t>DSO · Entity A1</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>CSH-006</t>
+          <t>WCP-001</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Entity A1</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>26 ₹ m</t>
+          <t>52 days</t>
         </is>
       </c>
       <c r="I129" s="21">
-        <f>'Owner KPIs'!K40</f>
+        <f>ROUND((IF('Entity Inputs'!AU9=0,0,'Entity Inputs'!CJ9/'Entity Inputs'!AU9*'Entity Inputs'!D9)),2)</f>
         <v/>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 40 (Group, Sep 2026)</t>
+          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20297,12 +20300,12 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>S-11</t>
+          <t>STATE GALLERY · O-01 + S-02</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Cash Exposure · how the supply issue reaches cash</t>
+          <t>Enterprise Health</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -20312,31 +20315,31 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>DSO · Entity A1</t>
+          <t>Production vs plan · Group MTD</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>WCP-001</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>Entity A1</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>52 days</t>
+          <t>98.1 % of plan</t>
         </is>
       </c>
       <c r="I130" s="21">
-        <f>ROUND((IF('Entity Inputs'!AU9=0,0,'Entity Inputs'!CJ9/'Entity Inputs'!AU9*'Entity Inputs'!D9)),2)</f>
+        <f>'Owner KPIs'!K2</f>
         <v/>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Entity Inputs row 9 (Entity A1, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20361,12 +20364,12 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Group MTD</t>
+          <t>EBITDA YTD (to P06)</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>FIN-001</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -20376,16 +20379,16 @@
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>98.1 % of plan</t>
+          <t>361.3 ₹ m</t>
         </is>
       </c>
       <c r="I131" s="21">
-        <f>'Owner KPIs'!K2</f>
+        <f>'Owner KPIs'!K29</f>
         <v/>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 29 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20410,12 +20413,12 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>EBITDA YTD (to P06)</t>
+          <t>Free Cash Flow YTD</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>FIN-001</t>
+          <t>FIN-004</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -20425,16 +20428,16 @@
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>361.3 ₹ m</t>
+          <t>96.4 ₹ m</t>
         </is>
       </c>
       <c r="I132" s="21">
-        <f>'Owner KPIs'!K29</f>
+        <f>'Owner KPIs'!K32</f>
         <v/>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 29 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 32 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20459,12 +20462,12 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Free Cash Flow YTD</t>
+          <t>Net Debt</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>FIN-004</t>
+          <t>FIN-006</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -20474,16 +20477,16 @@
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>96.4 ₹ m</t>
+          <t>1,140 ₹ m</t>
         </is>
       </c>
       <c r="I133" s="21">
-        <f>'Owner KPIs'!K32</f>
+        <f>'Owner KPIs'!K34</f>
         <v/>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 32 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 34 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20508,12 +20511,12 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>Net Debt</t>
+          <t>Capex physical progress</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>FIN-006</t>
+          <t>CPX-004</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -20523,16 +20526,16 @@
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>1,140 ₹ m</t>
+          <t>61 % weighted</t>
         </is>
       </c>
       <c r="I134" s="21">
-        <f>'Owner KPIs'!K34</f>
+        <f>'Owner KPIs'!K59</f>
         <v/>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 34 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 59 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20557,12 +20560,12 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Capex physical progress</t>
+          <t>Open critical alerts</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>CPX-004</t>
+          <t>EFF-002</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -20572,16 +20575,16 @@
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>61 % weighted</t>
+          <t>1 alert</t>
         </is>
       </c>
       <c r="I135" s="21">
-        <f>'Owner KPIs'!K59</f>
+        <f>'Owner KPIs'!K106</f>
         <v/>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 59 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 106 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20601,36 +20604,36 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>Open critical alerts</t>
+          <t>Days to breach · Plant 02 plan</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>EFF-002</t>
+          <t>PRD-001</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>1 alert</t>
+          <t>4 days</t>
         </is>
       </c>
       <c r="I136" s="21">
-        <f>'Owner KPIs'!K106</f>
+        <f>ROUND('Plant Inputs'!BT15,2)</f>
         <v/>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 106 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20655,31 +20658,31 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Days to breach · Plant 02 plan</t>
+          <t>Probability of plan miss · P07</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>PRD-001</t>
+          <t>PRD-002</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>4 days</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I137" s="21">
-        <f>ROUND('Plant Inputs'!BT15,2)</f>
+        <f>'Owner KPIs'!K114</f>
         <v/>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 114 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20704,12 +20707,12 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>Probability of plan miss · P07</t>
+          <t>Projected EBITDA gap · P07–P12</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>PRD-002</t>
+          <t>PRD-003</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -20719,16 +20722,16 @@
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>−₹9.2 m</t>
         </is>
       </c>
       <c r="I138" s="21">
-        <f>'Owner KPIs'!K114</f>
+        <f>'Owner KPIs'!K115</f>
         <v/>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 114 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20748,17 +20751,17 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Projected EBITDA gap · P07–P12</t>
+          <t>Capacity utilization</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>PRD-003</t>
+          <t>OPS-003</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -20768,16 +20771,16 @@
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>−₹9.2 m</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="I139" s="21">
-        <f>'Owner KPIs'!K115</f>
+        <f>'Owner KPIs'!K3</f>
         <v/>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20802,12 +20805,12 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Capacity utilization</t>
+          <t>Sales vs plan · MTD</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>OPS-003</t>
+          <t>OPS-002</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -20817,16 +20820,16 @@
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="I140" s="21">
-        <f>'Owner KPIs'!K3</f>
+        <f>'Owner KPIs'!K26</f>
         <v/>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 26 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20851,12 +20854,12 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Sales vs plan · MTD</t>
+          <t>EBIT YTD</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>OPS-002</t>
+          <t>FIN-002</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -20866,16 +20869,16 @@
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>238.4 ₹ m</t>
         </is>
       </c>
       <c r="I141" s="21">
-        <f>'Owner KPIs'!K26</f>
+        <f>'Owner KPIs'!K30</f>
         <v/>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 26 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 30 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20900,12 +20903,12 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>EBIT YTD</t>
+          <t>Revenue YTD</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>FIN-002</t>
+          <t>FIN-003</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -20915,16 +20918,16 @@
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>238.4 ₹ m</t>
+          <t>2,410 ₹ m</t>
         </is>
       </c>
       <c r="I142" s="21">
-        <f>'Owner KPIs'!K30</f>
+        <f>'Owner KPIs'!K31</f>
         <v/>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 30 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 31 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20949,12 +20952,12 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Revenue YTD</t>
+          <t>ROCE (rolling 12 m)</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>FIN-003</t>
+          <t>FIN-005</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -20964,16 +20967,16 @@
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>2,410 ₹ m</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="I143" s="21">
-        <f>'Owner KPIs'!K31</f>
+        <f>'Owner KPIs'!K33</f>
         <v/>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 31 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 33 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -20998,12 +21001,12 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>ROCE (rolling 12 m)</t>
+          <t>Shareholder-value indicator</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>FIN-005</t>
+          <t>FIN-007</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -21013,16 +21016,16 @@
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>[PLACEHOLDER]</t>
         </is>
       </c>
       <c r="I144" s="21">
-        <f>'Owner KPIs'!K33</f>
+        <f>'Owner KPIs'!K35</f>
         <v/>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 33 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 35 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21047,12 +21050,12 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Shareholder-value indicator</t>
+          <t>Transformation progress</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>FIN-007</t>
+          <t>STR-002</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -21062,16 +21065,16 @@
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER]</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="I145" s="21">
-        <f>'Owner KPIs'!K35</f>
+        <f>'Owner KPIs'!K65</f>
         <v/>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 35 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 65 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21096,12 +21099,12 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Transformation progress</t>
+          <t>Regulatory breaches · YTD</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>STR-002</t>
+          <t>RSK-003</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -21111,16 +21114,16 @@
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I146" s="21">
-        <f>'Owner KPIs'!K65</f>
+        <f>'Owner KPIs'!K79</f>
         <v/>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 65 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 79 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21130,7 +21133,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>STATE GALLERY · O-01 + S-02</t>
+          <t>O-01 · large display ≥ 1600</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -21140,17 +21143,17 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Regulatory breaches · YTD</t>
+          <t>Production vs plan · Group MTD</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>RSK-003</t>
+          <t>OPS-001</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -21160,16 +21163,16 @@
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98.1 % of plan</t>
         </is>
       </c>
       <c r="I147" s="21">
-        <f>'Owner KPIs'!K79</f>
+        <f>'Owner KPIs'!K2</f>
         <v/>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 79 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21194,12 +21197,12 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Production vs plan · Group MTD</t>
+          <t>EBITDA YTD (to P06)</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>OPS-001</t>
+          <t>FIN-001</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -21209,16 +21212,16 @@
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>98.1 % of plan</t>
+          <t>361.3 ₹ m</t>
         </is>
       </c>
       <c r="I148" s="21">
-        <f>'Owner KPIs'!K2</f>
+        <f>'Owner KPIs'!K29</f>
         <v/>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 2 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 29 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21243,12 +21246,12 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>EBITDA YTD (to P06)</t>
+          <t>Free Cash Flow YTD</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>FIN-001</t>
+          <t>FIN-004</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -21258,16 +21261,16 @@
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>361.3 ₹ m</t>
+          <t>96.4 ₹ m</t>
         </is>
       </c>
       <c r="I149" s="21">
-        <f>'Owner KPIs'!K29</f>
+        <f>'Owner KPIs'!K32</f>
         <v/>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 29 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 32 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21292,12 +21295,12 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Free Cash Flow YTD</t>
+          <t>Net Debt</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>FIN-004</t>
+          <t>FIN-006</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -21307,16 +21310,16 @@
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>96.4 ₹ m</t>
+          <t>1,140 ₹ m</t>
         </is>
       </c>
       <c r="I150" s="21">
-        <f>'Owner KPIs'!K32</f>
+        <f>'Owner KPIs'!K34</f>
         <v/>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 32 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 34 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21341,12 +21344,12 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Net Debt</t>
+          <t>Capex physical progress</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>FIN-006</t>
+          <t>CPX-004</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -21356,16 +21359,16 @@
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>1,140 ₹ m</t>
+          <t>61 % weighted</t>
         </is>
       </c>
       <c r="I151" s="21">
-        <f>'Owner KPIs'!K34</f>
+        <f>'Owner KPIs'!K59</f>
         <v/>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 34 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 59 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21390,12 +21393,12 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Capex physical progress</t>
+          <t>Open critical alerts</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>CPX-004</t>
+          <t>EFF-002</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -21405,16 +21408,16 @@
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>61 % weighted</t>
+          <t>1 alert</t>
         </is>
       </c>
       <c r="I152" s="21">
-        <f>'Owner KPIs'!K59</f>
+        <f>'Owner KPIs'!K106</f>
         <v/>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 59 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 106 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21434,36 +21437,36 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Tile</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Open critical alerts</t>
+          <t>Days to breach · Plant 02 plan</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>EFF-002</t>
+          <t>PRD-001</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Plant 02</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>1 alert</t>
+          <t>4 days</t>
         </is>
       </c>
       <c r="I153" s="21">
-        <f>'Owner KPIs'!K106</f>
+        <f>ROUND('Plant Inputs'!BT15,2)</f>
         <v/>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 106 (Group, Sep 2026)</t>
+          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21488,31 +21491,31 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Days to breach · Plant 02 plan</t>
+          <t>Probability of plan miss · P07</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>PRD-001</t>
+          <t>PRD-002</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>Plant 02</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>4 days</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I154" s="21">
-        <f>ROUND('Plant Inputs'!BT15,2)</f>
+        <f>'Owner KPIs'!K114</f>
         <v/>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>Same formula on Plant Inputs row 15 (Plant 02, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 114 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21537,12 +21540,12 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Probability of plan miss · P07</t>
+          <t>Projected EBITDA gap · P07–P12</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>PRD-002</t>
+          <t>PRD-003</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -21552,16 +21555,16 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>−₹9.2 m</t>
         </is>
       </c>
       <c r="I155" s="21">
-        <f>'Owner KPIs'!K114</f>
+        <f>'Owner KPIs'!K115</f>
         <v/>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 114 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21581,17 +21584,17 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Tile</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Projected EBITDA gap · P07–P12</t>
+          <t>Capacity utilization</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>PRD-003</t>
+          <t>OPS-003</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -21601,16 +21604,16 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>−₹9.2 m</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="I156" s="21">
-        <f>'Owner KPIs'!K115</f>
+        <f>'Owner KPIs'!K3</f>
         <v/>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 115 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21635,12 +21638,12 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Capacity utilization</t>
+          <t>Sales vs plan · MTD</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>OPS-003</t>
+          <t>OPS-002</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -21650,16 +21653,16 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="I157" s="21">
-        <f>'Owner KPIs'!K3</f>
+        <f>'Owner KPIs'!K26</f>
         <v/>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 3 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 26 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21684,12 +21687,12 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Sales vs plan · MTD</t>
+          <t>EBIT YTD</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>OPS-002</t>
+          <t>FIN-002</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -21699,16 +21702,16 @@
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>238.4 ₹ m</t>
         </is>
       </c>
       <c r="I158" s="21">
-        <f>'Owner KPIs'!K26</f>
+        <f>'Owner KPIs'!K30</f>
         <v/>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 26 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 30 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21733,12 +21736,12 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>EBIT YTD</t>
+          <t>Revenue YTD</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>FIN-002</t>
+          <t>FIN-003</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -21748,16 +21751,16 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>238.4 ₹ m</t>
+          <t>2,410 ₹ m</t>
         </is>
       </c>
       <c r="I159" s="21">
-        <f>'Owner KPIs'!K30</f>
+        <f>'Owner KPIs'!K31</f>
         <v/>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 30 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 31 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21782,12 +21785,12 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Revenue YTD</t>
+          <t>ROCE (rolling 12 m)</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>FIN-003</t>
+          <t>FIN-005</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -21797,16 +21800,16 @@
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>2,410 ₹ m</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="I160" s="21">
-        <f>'Owner KPIs'!K31</f>
+        <f>'Owner KPIs'!K33</f>
         <v/>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 31 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 33 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21831,12 +21834,12 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>ROCE (rolling 12 m)</t>
+          <t>Shareholder-value indicator</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>FIN-005</t>
+          <t>FIN-007</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -21846,16 +21849,16 @@
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>[PLACEHOLDER]</t>
         </is>
       </c>
       <c r="I161" s="21">
-        <f>'Owner KPIs'!K33</f>
+        <f>'Owner KPIs'!K35</f>
         <v/>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 33 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 35 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21880,12 +21883,12 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Shareholder-value indicator</t>
+          <t>Transformation progress</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>FIN-007</t>
+          <t>STR-002</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -21895,16 +21898,16 @@
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>[PLACEHOLDER]</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="I162" s="21">
-        <f>'Owner KPIs'!K35</f>
+        <f>'Owner KPIs'!K65</f>
         <v/>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>Owner KPIs sheet, row 35 (Group, Sep 2026)</t>
+          <t>Owner KPIs sheet, row 65 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -21929,12 +21932,12 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Transformation progress</t>
+          <t>Regulatory breaches · YTD</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>STR-002</t>
+          <t>RSK-003</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -21944,70 +21947,21 @@
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I163" s="21">
-        <f>'Owner KPIs'!K65</f>
+        <f>'Owner KPIs'!K79</f>
         <v/>
       </c>
       <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>Owner KPIs sheet, row 65 (Group, Sep 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="n">
-        <v>163</v>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>O-01 · large display ≥ 1600</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise Health</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>Regulatory breaches · YTD</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>RSK-003</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I164" s="21">
-        <f>'Owner KPIs'!K79</f>
-        <v/>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
         <is>
           <t>Owner KPIs sheet, row 79 (Group, Sep 2026)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J164"/>
+  <autoFilter ref="A1:J163"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
